--- a/workspaces/btc_daily_14days/dxy/dxy_ret_20.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_20.xlsx
@@ -575,46 +575,46 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.0065616797886</v>
+        <v>9.971882511943306</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.399083578724806</v>
+        <v>8.370414995428696</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.751482802799046</v>
+        <v>1.741938704814231</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20.63970403893536</v>
+        <v>20.57438321623466</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20.10113766648232</v>
+        <v>20.03683294546619</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>20.40804218337402</v>
+        <v>20.34277079574625</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.07378510804686</v>
+        <v>14.0291586850888</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.351085473987375</v>
+        <v>7.327269068505295</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13.55909983961866</v>
+        <v>13.51342676269568</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.442792919658459</v>
+        <v>6.419774271638957</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.235542092843801</v>
+        <v>6.216019948319925</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.270549625812436</v>
+        <v>6.250153355417496</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4162813877858227</v>
+        <v>-0.4139391433515058</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.10482295840643</v>
+        <v>6.085447582576819</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>24</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-14.99343832020902</v>
+        <v>-14.94792680293396</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.106617058762119</v>
+        <v>-4.0953811796441</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.835804061748298</v>
+        <v>3.819344484443981</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.965508072444955</v>
+        <v>3.952892348522241</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.426939016856544</v>
+        <v>3.415358176537119</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-12.9557676677376</v>
+        <v>-12.91437124314538</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-17.21922366882941</v>
+        <v>-17.16349627907287</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.346179199010969</v>
+        <v>-9.316449093411073</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.233698796930774</v>
+        <v>-5.219453782685967</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.085837786055805</v>
+        <v>-6.068773446074104</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.293134862918052</v>
+        <v>-6.272509269375142</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.25811576743574</v>
+        <v>-6.238380487285035</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.86193383746694</v>
+        <v>-10.82577484618464</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-10.61554697592965</v>
+        <v>-10.58121908409032</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>23</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.667351363689221</v>
+        <v>-4.654586609897621</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.767989786051743</v>
+        <v>6.743934273203152</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.023415332976271</v>
+        <v>2.012517436793061</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.502964121593621</v>
+        <v>6.481779242035124</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.964391820559698</v>
+        <v>5.944264542741365</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.264817753202458</v>
+        <v>6.244310132046969</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.5365171750523</v>
+        <v>10.50276230589491</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.0737710854693</v>
+        <v>10.04068964250167</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.303075649447919</v>
+        <v>1.29627122137066</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.808891189789442</v>
+        <v>4.790726267933891</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2435393470739484</v>
+        <v>0.2432558292377252</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.994570068954317</v>
+        <v>8.964893004248026</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>17.29596992641211</v>
+        <v>17.24090302891829</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.19339084198849</v>
+        <v>13.15066497387974</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>23</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-13.3630035375993</v>
+        <v>-13.32123607314777</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-23.68108777237008</v>
+        <v>-23.60507863712167</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-15.3760663942654</v>
+        <v>-15.32972263453951</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-10.89648568866249</v>
+        <v>-10.86065233121472</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.73530350123302</v>
+        <v>-2.727128743905482</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.43892217489708</v>
+        <v>-2.431122656400305</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.525139243498799</v>
+        <v>-2.516478411403888</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.350013474192387</v>
+        <v>-7.326254546445988</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.661290905989716</v>
+        <v>5.639941640493461</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.167283018405612</v>
+        <v>9.134326058228922</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>13.31787224696504</v>
+        <v>13.27439223449768</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>8.995031328914038</v>
+        <v>8.964708500263754</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>12.93682545449308</v>
+        <v>12.89496333945387</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>17.55655791973028</v>
+        <v>17.49849106083528</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>34</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.271267562142967</v>
+        <v>9.238186512339773</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>16.49133541264528</v>
+        <v>16.43455105072953</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>24.92441130218749</v>
+        <v>24.8367206496491</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.34118178107301</v>
+        <v>10.30669323400559</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.802647287802429</v>
+        <v>9.768951688124531</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>18.9370201261239</v>
+        <v>18.87326711533876</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>18.86102947024262</v>
+        <v>18.79812698647643</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>21.34917504287696</v>
+        <v>21.27723130360318</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12.45549445834138</v>
+        <v>12.41075126814648</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>14.55168279617466</v>
+        <v>14.49974773279587</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.29244701917216</v>
+        <v>17.23443444837712</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>14.3793795457303</v>
+        <v>14.33015079921407</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>16.91344427694734</v>
+        <v>16.85708697134771</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>14.22214249481324</v>
+        <v>14.17368287669305</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>50</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.506561679789108</v>
+        <v>5.485064970523013</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.897246223272028</v>
+        <v>3.881439128150028</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.504603588992609</v>
+        <v>7.473213987647227</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.634172574745719</v>
+        <v>7.607572001383296</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.092683550812069</v>
+        <v>1.087557639481417</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>7.397018714950292</v>
+        <v>7.370329466805316</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6961006733413555</v>
+        <v>-0.6943269397265937</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.167907064133665</v>
+        <v>-3.158486527904365</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7810707566316992</v>
+        <v>0.7746383958891414</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.933977022911151</v>
+        <v>1.923300630338801</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.731426237433837</v>
+        <v>3.717666290484388</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.761593782804916</v>
+        <v>1.753735692619472</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.6717184707977</v>
+        <v>-2.663032962851496</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.599367240568426</v>
+        <v>3.585447582575398</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>66</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-4.00858983536132</v>
+        <v>-3.997525629274378</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.472921331408905</v>
+        <v>3.457691509628631</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.626141616027518</v>
+        <v>7.592470673928133</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.723827457622143</v>
+        <v>4.706006340486148</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.217049206472495</v>
+        <v>7.189848554001799</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>9.035495866927192</v>
+        <v>9.001409314136026</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.885068445054706</v>
+        <v>2.874215245846123</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.455354455643281</v>
+        <v>5.434673392870387</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.399128954374277</v>
+        <v>5.375899965276929</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.104149094559574</v>
+        <v>9.067353013799519</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.377627922714112</v>
+        <v>7.350094707281528</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.412638130514367</v>
+        <v>7.384227044444408</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.47387657709826</v>
+        <v>5.454115337246897</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.687855864588414</v>
+        <v>2.676356673484491</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>87</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3801248981809664</v>
+        <v>0.3757649918326251</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.531668611059395</v>
+        <v>-3.5220833601172</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.626032378932337</v>
+        <v>-1.628027676067532</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.403601477532661</v>
+        <v>5.381803182362461</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.03519997298708</v>
+        <v>-2.030198688991938</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5873136684521683</v>
+        <v>-0.588379804574565</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.629526694989025</v>
+        <v>1.62246109023917</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.140776309541067</v>
+        <v>-1.138604708790226</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.562308953254615</v>
+        <v>4.540304036780029</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.863043331886232</v>
+        <v>4.839030428587847</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.807657612073207</v>
+        <v>5.783725464766761</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.2327703108176</v>
+        <v>1.225035196357467</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.575945781568549</v>
+        <v>6.550478933784895</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.09061367323893421</v>
+        <v>-0.09271333696483453</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>91</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.748319921548273</v>
+        <v>5.722545482260884</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.55708098536072</v>
+        <v>-3.546443773900116</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.645674970942103</v>
+        <v>2.626785695951732</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8.27276065124979</v>
+        <v>8.237582003898076</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.833498044892082</v>
+        <v>8.796516828846045</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>9.136850757759618</v>
+        <v>9.09767243670511</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.653713546624026</v>
+        <v>4.634125895192163</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8.594117397809413</v>
+        <v>8.558456664100603</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.439150156725717</v>
+        <v>7.403714328159076</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.281451728599059</v>
+        <v>3.261233824985752</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.379349685826512</v>
+        <v>6.350804603435193</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.41388199352194</v>
+        <v>6.385128100640436</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.687356684332642</v>
+        <v>2.674557075396208</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>6.249900021018782</v>
+        <v>6.222810219937912</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>99</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.98838781515947</v>
+        <v>-1.985048891153276</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.612376377748184</v>
+        <v>-4.596178801084314</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.006452191309265</v>
+        <v>-4.995804865893362</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.855463103795962</v>
+        <v>-2.848553321307783</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.46913617503367</v>
+        <v>-10.43041289433592</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-7.142651426466756</v>
+        <v>-7.118879018036075</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-9.256120497681522</v>
+        <v>-9.220361113334036</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.678650350709944</v>
+        <v>-5.659267446809537</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.75245908920855</v>
+        <v>-6.733161786986912</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.565623186878788</v>
+        <v>-4.555647164533646</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.786624322712257</v>
+        <v>-5.768042778386466</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.738980427786444</v>
+        <v>-4.724822501931662</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.151067885019302</v>
+        <v>-4.137013447686556</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.901164220812092</v>
+        <v>-3.889299892171962</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>95</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.296035364000545</v>
+        <v>3.276617111427292</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.527354009536026</v>
+        <v>-2.518327896056029</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.974624566411855</v>
+        <v>-3.967206553609245</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.527999469800079</v>
+        <v>3.507768525793082</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.148784668159458</v>
+        <v>6.119371988026245</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.343529125639755</v>
+        <v>4.319842913764326</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7.424069612020624</v>
+        <v>7.39106004821236</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.74087988159436</v>
+        <v>2.72571273648429</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.741240837538548</v>
+        <v>3.716886153000033</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7771926070271249</v>
+        <v>0.7649617651128509</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.736528612144703</v>
+        <v>3.715625340600219</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.883159276641756</v>
+        <v>5.852477916137516</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.237196981016766</v>
+        <v>1.229340777635599</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6240198742082512</v>
+        <v>-0.6250787332140817</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>111</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.263318436546783</v>
+        <v>4.236651771094969</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>6.259793519350616</v>
+        <v>6.228677874199995</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.865895252320811</v>
+        <v>5.827986530201507</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.192669125308797</v>
+        <v>4.166502607914175</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>10.86567556026066</v>
+        <v>10.80996594314743</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.955134682978425</v>
+        <v>3.929994501690004</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.872155409933711</v>
+        <v>3.851301585876435</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.214362970514799</v>
+        <v>5.185441576740637</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.449595613678369</v>
+        <v>2.427949173791035</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.115113724482121</v>
+        <v>-1.120126133767606</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4844126821237893</v>
+        <v>0.4759311720678525</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.231471394920455</v>
+        <v>3.209027891016575</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.713753554787935</v>
+        <v>3.693142119971483</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.873812758957754</v>
+        <v>4.846708843836652</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>152</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.111824837684757</v>
+        <v>2.091190497703806</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.473908915527268</v>
+        <v>-1.470577407477514</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1075491283570216</v>
+        <v>0.0923828567254219</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.029960719121348</v>
+        <v>-5.012891393310355</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.20228868307634</v>
+        <v>-8.168924746664246</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.250386584180468</v>
+        <v>-7.221683601157793</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.703927680399801</v>
+        <v>-4.683890930315016</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-9.133128549848657</v>
+        <v>-9.092465150459418</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-8.535661550882892</v>
+        <v>-8.503931838999812</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.748371716934948</v>
+        <v>-6.724812505302303</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.956935534742016</v>
+        <v>-6.928041632224087</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-8.241513919783699</v>
+        <v>-8.208179121081642</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.368182557049849</v>
+        <v>-5.345201229177896</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.473289516220454</v>
+        <v>-2.467183996371972</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>165</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.26413743736579</v>
+        <v>3.231007567896633</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>8.32700952175361</v>
+        <v>8.272556306955565</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.771461143863228</v>
+        <v>-1.779488524307389</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.996920154036026</v>
+        <v>1.976541071095923</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.670951413850972</v>
+        <v>2.64825349154971</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.098777123589912</v>
+        <v>-3.087150633814318</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1491127335579563</v>
+        <v>-0.1509169200437839</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.815097679713439</v>
+        <v>1.801229611180865</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.499242271080192</v>
+        <v>-2.495054574844403</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-6.396565836787239</v>
+        <v>-6.368724650024959</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.388839473723444</v>
+        <v>-5.361500152325405</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.352840239385593</v>
+        <v>-5.327763425776858</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.954786539545495</v>
+        <v>-3.9340367695753</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.092689229934685</v>
+        <v>-3.081219084091266</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>133</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.117498470585915</v>
+        <v>-2.123795569539801</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.795367365280377</v>
+        <v>3.755870170834982</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.401325870648613</v>
+        <v>3.356038192449752</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7.293368950627851</v>
+        <v>7.23134111450986</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.743778632532013</v>
+        <v>3.707302938631848</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.98114761950989</v>
+        <v>-1.973728381255036</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.964182763188994</v>
+        <v>3.934067074724311</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.500805247728849</v>
+        <v>3.471558185567993</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.4258395297417792</v>
+        <v>0.4114677287502602</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.5907357493559</v>
+        <v>2.565860297655057</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.158196440232764</v>
+        <v>6.115379261996623</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.6836106639999</v>
+        <v>4.648086834878384</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.993893176266639</v>
+        <v>1.98041772755014</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.010411516876374</v>
+        <v>2.983943823176901</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.967890874954499</v>
+        <v>-7.970913071346644</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-7.394793732567614</v>
+        <v>-7.397687045244773</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.327106823686584</v>
+        <v>-6.328470553513071</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.544230401284644</v>
+        <v>-2.543902252405637</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.084050323090977</v>
+        <v>-3.08451408905421</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.058791417117455</v>
+        <v>-2.05962062732754</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.608938761313397</v>
+        <v>-3.610540808681584</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.415129267113414</v>
+        <v>-4.417038569813514</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.680600859990307</v>
+        <v>-6.683564847108777</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.594359531790616</v>
+        <v>-4.596268343077867</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.53008087033966</v>
+        <v>-5.532938712860513</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-7.696098429469508</v>
+        <v>-7.700158796229303</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-7.387087135485068</v>
+        <v>-7.391577866108641</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-10.08555907790914</v>
+        <v>-10.09102300565989</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-11.5212160979878</v>
+        <v>-11.60034949087823</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-9.670594027056737</v>
+        <v>-9.736543229855307</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-13.54051774012872</v>
+        <v>-13.62509948160664</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.543444851532094</v>
+        <v>-8.590478182333158</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.520862375656641</v>
+        <v>-3.532060787752101</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.139969946266426</v>
+        <v>-1.1451838498825</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.922509849140994</v>
+        <v>-1.93335636291625</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.095490442131556</v>
+        <v>1.113061794447589</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.806277975067751</v>
+        <v>2.841677117947292</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.353581909326067</v>
+        <v>3.392394734887404</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.45461320074871</v>
+        <v>2.478617565849333</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.791781523578791</v>
+        <v>1.809711840965228</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.868555104070801</v>
+        <v>3.895025450708857</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.319666831863032</v>
+        <v>1.331926455814838</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.393779724902856</v>
+        <v>2.402197194236919</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.290704160324516</v>
+        <v>2.298709606729197</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.650420888341849</v>
+        <v>2.662997387674871</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5218297909853575</v>
+        <v>0.5289915593717893</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.7707497218417103</v>
+        <v>-0.7674374039630365</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.033187188267128</v>
+        <v>1.037154078187676</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.9504637624173995</v>
+        <v>0.9542404137461915</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.270309885833754</v>
+        <v>-0.2674964988972661</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.594658460135477</v>
+        <v>-2.596186584950651</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.693771335404406</v>
+        <v>-2.695787914401514</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.6383983962407598</v>
+        <v>-0.6378881117042781</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.115707132328083</v>
+        <v>-2.119663884081618</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4796882244607943</v>
+        <v>0.4803103895641385</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.109475525926783</v>
+        <v>-1.111522114394305</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-5.590783452953339</v>
+        <v>-5.611746079576726</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.667210351459076</v>
+        <v>-3.679026345321994</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5127519787821271</v>
+        <v>-0.5005532232703587</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.156211417725849</v>
+        <v>-2.153617144328258</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.03644119568497928</v>
+        <v>-0.02544743054906462</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.037473390207779</v>
+        <v>2.051259574927101</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.874017915509391</v>
+        <v>6.911802355350751</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.628345089018417</v>
+        <v>4.658904670854959</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.565749178977043</v>
+        <v>4.597904784672657</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.055071959750485</v>
+        <v>1.069208171073299</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.744351420864717</v>
+        <v>1.757311989612816</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.558022017849211</v>
+        <v>3.577409432672582</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.031002180406681</v>
+        <v>4.050011964584819</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.277531464964866</v>
+        <v>4.299733296861064</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>97</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.114809102470439</v>
+        <v>1.107307262405698</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.604180975767697</v>
+        <v>2.587857013553972</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.985557325775488</v>
+        <v>-3.983276118714706</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.890177232638344</v>
+        <v>-4.880005616739879</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-9.563780013029358</v>
+        <v>-9.530667946905609</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.144460466861901</v>
+        <v>-5.126070702045546</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.26034023645979</v>
+        <v>-6.241732254369431</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.691566883921212</v>
+        <v>-5.677987818099382</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.786599241825755</v>
+        <v>-6.769915539333233</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-8.681340436364003</v>
+        <v>-8.650968559412711</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-10.96378010211514</v>
+        <v>-10.91757755383332</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.714618576648149</v>
+        <v>-4.697627386178695</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.139683886587541</v>
+        <v>-5.117881997123575</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.814200492475507</v>
+        <v>-2.80630499474416</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>75</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-5.826771653543346</v>
+        <v>-5.796906000964405</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.106662958547851</v>
+        <v>-2.103360907800578</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1774163130736142</v>
+        <v>0.1561557407181908</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.979376084541052</v>
+        <v>2.948035567799053</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.435885931918151</v>
+        <v>2.414683290277544</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.741753365947368</v>
+        <v>2.722726548813505</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.345431249209035</v>
+        <v>5.30465949820789</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.826763677299738</v>
+        <v>-1.829190567240275</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5450138971793379</v>
+        <v>-0.5568571200892478</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.296767239841003</v>
+        <v>5.259684361549489</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.421658376147086</v>
+        <v>6.388264370565253</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.463322203314256</v>
+        <v>6.422647527910748</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.035786922547615</v>
+        <v>6.002392916965782</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.976832123286542</v>
+        <v>8.918780915908769</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>73</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.301082227735272</v>
+        <v>2.286116095538091</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-3.42766080625541</v>
+        <v>-3.41250004639442</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.438404843660408</v>
+        <v>-2.451767394785385</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.810701447026297</v>
+        <v>-7.777868635793538</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-6.981972463303364</v>
+        <v>-6.943714022263507</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.186011679942311</v>
+        <v>-1.185949250273254</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.017713266224661</v>
+        <v>-4.010408994942793</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3530514468846775</v>
+        <v>-0.3680033526284063</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.170133933762195</v>
+        <v>-3.168729266207968</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1093074164100756</v>
+        <v>0.09073458985999849</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.02956326145015</v>
+        <v>3.995570306638349</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.445940099673528</v>
+        <v>-1.449498590810819</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.643691807850679</v>
+        <v>3.609698853038878</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.15100263695944</v>
+        <v>1.119694157917863</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.038892865664522</v>
+        <v>-7.296182745595885</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.682613039292441</v>
+        <v>-7.93957682305156</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.866973622833406</v>
+        <v>-0.7227086762153618</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.941122579252173</v>
+        <v>3.138084667311155</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>11.5350898882035</v>
+        <v>11.99058102164857</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.696124651982558</v>
+        <v>3.879959253216015</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.353216976462512</v>
+        <v>-7.525529181037392</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.80652112472351</v>
+        <v>-7.992712579818892</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-4.231157374542185</v>
+        <v>-4.280127560340816</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.05352405852917</v>
+        <v>-5.130252745368743</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-7.020942198946706</v>
+        <v>-7.221798522516593</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-7.000438292121686</v>
+        <v>-7.187415365171084</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.770450016182515</v>
+        <v>-3.834085070455664</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-9.058549641574501</v>
+        <v>-9.244741096669884</v>
       </c>
     </row>
     <row r="29">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.03209</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2198~2205</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2198</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.838109522024034</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.02982</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2182~2189</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2182</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.9173761913840224</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.02755</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2158~2165</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2158</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.7613367035817973</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.02528</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2135~2142</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2135</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.7193953696964286</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2112~2119</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2112</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.5821594150660445</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.02073</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2078~2085</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2078</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.7428387998262878</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.01846</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2028~2035</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2028</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.896386723158372</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.01619</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1962~1969</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1962</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.7920670657660906</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.01392</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1875~1882</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1875</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.8462544732386661</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.01164</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1784~1791</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1784</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.181322183973236</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.009372</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1685~1692</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1685</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.134100258744255</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.007099</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1590~1597</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1590</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.397633686521807</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.004827</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1479~1486</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1479</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.820490810115764</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.002555</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1327~1334</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1327</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-2.268550763988088</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.0002829</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1162~1169</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1162</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-3.049469115761731</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.001989</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1029~1036</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1029</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-3.169113995885652</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.004261</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>893~899</t>
-        </is>
+      <c r="B22" t="n">
+        <v>893</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-2.437820967595961</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.006534</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>751~755</t>
-        </is>
+      <c r="B23" t="n">
+        <v>751</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.7053588500112937</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.008806</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>619~622</t>
-        </is>
+      <c r="B24" t="n">
+        <v>619</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.368036390949527</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.01108</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>507~509</t>
-        </is>
+      <c r="B25" t="n">
+        <v>507</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.4305699508583061</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.01335</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>410~412</t>
-        </is>
+      <c r="B26" t="n">
+        <v>410</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.7944091939963869</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.01562</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>335~337</t>
-        </is>
+      <c r="B27" t="n">
+        <v>335</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.325552777712879</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.01789</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>262~264</t>
-        </is>
+      <c r="B28" t="n">
+        <v>262</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.2207110474827019</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.02017</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>209~209</t>
-        </is>
+      <c r="B29" t="n">
+        <v>209</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.573547325723041</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.02244</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>172~172</t>
-        </is>
+      <c r="B30" t="n">
+        <v>172</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.157724470487693</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.02471</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>124~124</t>
-        </is>
+      <c r="B31" t="n">
+        <v>124</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>3.151722970112601</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.02698</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>89~89</t>
-        </is>
+      <c r="B32" t="n">
+        <v>89</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.439145949452943</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.02926</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>64~64</t>
-        </is>
+      <c r="B33" t="n">
+        <v>64</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.9309383202099752</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.03153</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>56~56</t>
-        </is>
+      <c r="B34" t="n">
+        <v>56</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.0338</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>46~46</t>
-        </is>
+      <c r="B35" t="n">
+        <v>46</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.03209</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>46~46</t>
-        </is>
+      <c r="B6" t="n">
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.02982</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>62~62</t>
-        </is>
+      <c r="B7" t="n">
+        <v>62</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.7323681314029216</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.02755</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>86~86</t>
-        </is>
+      <c r="B8" t="n">
+        <v>86</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-3.656229017884399</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.02528</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>109~109</t>
-        </is>
+      <c r="B9" t="n">
+        <v>109</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-3.869585109200798</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>132~132</t>
-        </is>
+      <c r="B10" t="n">
+        <v>132</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-5.523741350513006</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.02073</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>166~166</t>
-        </is>
+      <c r="B11" t="n">
+        <v>166</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.01846</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>216~216</t>
-        </is>
+      <c r="B12" t="n">
+        <v>216</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.6415864683581276</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.01619</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>282~282</t>
-        </is>
+      <c r="B13" t="n">
+        <v>282</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.429608532975934</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.01392</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>369~369</t>
-        </is>
+      <c r="B14" t="n">
+        <v>369</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-1.00292341506092</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.01164</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>460~460</t>
-        </is>
+      <c r="B15" t="n">
+        <v>460</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.3326486363117596</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.009372</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>559~559</t>
-        </is>
+      <c r="B16" t="n">
+        <v>559</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.07841148657848862</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.007099</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>654~654</t>
-        </is>
+      <c r="B17" t="n">
+        <v>654</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.4117604565484356</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.004827</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>765~765</t>
-        </is>
+      <c r="B18" t="n">
+        <v>765</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.970613967371726</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.002555</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>917~917</t>
-        </is>
+      <c r="B19" t="n">
+        <v>917</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.159778691785661</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.0002829</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1082~1082</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1082</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.480683676093165</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.001989</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1215~1215</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1215</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.086808593370264</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.004261</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1351~1352</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1351</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.1692835732811488</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.006534</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1493~1496</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1493</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.9560051651297599</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.008806</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1625~1629</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1625</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.6825113711614819</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.01108</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1737~1742</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1737</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.000901006777134</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.01335</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1834~1839</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1834</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.8893056394051939</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.01562</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1909~1914</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1909</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.08278001299994</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.01789</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1982~1987</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1982</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.9584609674168192</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.02017</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2035~2042</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2035</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.122233618936711</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.02244</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2072~2079</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2072</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.122586949358606</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.02471</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2120~2127</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2120</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.106508371926012</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.02698</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2155~2162</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2155</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.9670738428741785</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.02926</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2180~2187</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2180</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.8702101537719358</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.03153</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2188~2195</t>
-        </is>
+      <c r="B34" t="n">
+        <v>2188</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.8305681607566768</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.0338</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2198~2205</t>
-        </is>
+      <c r="B35" t="n">
+        <v>2198</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.838109522024034</v>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_20.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_20.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-20 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-20 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,1509 +568,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.03095</t>
+          <t>X ≈ -0.03106</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.971882511943306</v>
+        <v>9.028671230991314</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.370414995428696</v>
+        <v>3.589731124105562</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.741938704814231</v>
+        <v>-12.14644883956036</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>20.57438321623466</v>
+        <v>-12.01946104607091</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20.03683294546619</v>
+        <v>-4.884446628347817</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>20.34277079574625</v>
+        <v>-0.7503204678928839</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>14.0291586850888</v>
+        <v>-0.8349321627706416</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.327269068505295</v>
+        <v>-8.982453649469669</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13.51342676269568</v>
+        <v>-1.362714118529397</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>6.419774271638957</v>
+        <v>-9.896799495949907</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.216019948319925</v>
+        <v>-6.260456215273273</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.250153355417496</v>
+        <v>-2.383349113462884</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4139391433515058</v>
+        <v>-10.49432665677489</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.085447582576819</v>
+        <v>-6.424982053120999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02869</t>
+          <t>X ≈ -0.0288</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-14.94792680293396</v>
+        <v>-9.948697198586522</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.0953811796441</v>
+        <v>-4.079780753580103</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.819344484443981</v>
+        <v>-4.474662563077992</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.952892348522241</v>
+        <v>-1.852041679925605</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.415358176537119</v>
+        <v>-2.389876801378762</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-12.91437124314538</v>
+        <v>-14.56886755373438</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-17.16349627907287</v>
+        <v>-14.65692021403872</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.316449093411073</v>
+        <v>-7.638097979064476</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.219453782685967</v>
+        <v>-5.204050682346995</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-6.068773446074104</v>
+        <v>-3.556816463701551</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.272509269375142</v>
+        <v>-6.260382334985493</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.238380487285035</v>
+        <v>-3.72881387893257</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-10.82577484618464</v>
+        <v>-6.649090522926819</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-10.58121908409032</v>
+        <v>-3.924982053122754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02642</t>
+          <t>X ≈ -0.02654</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.654586609897621</v>
+        <v>-5.523730956974973</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.743934273203152</v>
+        <v>1.007114499053401</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.012517436793061</v>
+        <v>0.613511870065615</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.481779242035124</v>
+        <v>0.7435448991986036</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.944264542741365</v>
+        <v>0.206374267535324</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.244310132046969</v>
+        <v>6.613453320197756</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.50276230589491</v>
+        <v>6.530667962814796</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.04068964250167</v>
+        <v>8.103597891228311</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.29627122137066</v>
+        <v>6.00641841448985</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.790726267933891</v>
+        <v>9.236454028454972</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2432558292377252</v>
+        <v>2.916438081382921</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.964893004248026</v>
+        <v>2.951523395376398</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>17.24090302891829</v>
+        <v>0.4919989922233086</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.15066497387974</v>
+        <v>-5.404573889857446</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02414</t>
+          <t>X ≈ -0.02428</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-13.32123607314777</v>
+        <v>2.773543535617826</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-23.60507863712167</v>
+        <v>-11.95006101618186</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-15.32972263453951</v>
+        <v>-12.34693393103856</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-10.86065233121472</v>
+        <v>-12.22020297818217</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.727128743905482</v>
+        <v>-7.509546542995906</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.431122656400305</v>
+        <v>-9.840913039903306</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.516478411403888</v>
+        <v>-2.04718158296123</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.326254546445988</v>
+        <v>-5.141709236782845</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.639941640493461</v>
+        <v>0.05250886451314329</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.134326058228922</v>
+        <v>1.832414396169398</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>13.27439223449768</v>
+        <v>4.258002861192395</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>8.964708500263754</v>
+        <v>1.66320893351044</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>12.89496333945387</v>
+        <v>6.505499412909671</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>17.49849106083528</v>
+        <v>6.732912683719348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02186</t>
+          <t>X ≈ -0.02202</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.238186512339773</v>
+        <v>2.734162068309189</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>16.43455105072953</v>
+        <v>2.616728361900883</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>24.8367206496491</v>
+        <v>9.665010072300653</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.30669323400559</v>
+        <v>2.353976000745583</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9.768951688124531</v>
+        <v>4.795245356101908</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>18.87326711533876</v>
+        <v>9.561603623831743</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>18.79812698647643</v>
+        <v>9.479498419195906</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>21.27723130360318</v>
+        <v>6.035123763643647</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12.41075126814648</v>
+        <v>4.485082571017074</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>14.49974773279587</v>
+        <v>6.619218642410729</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.23443444837712</v>
+        <v>7.907857939815642</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>14.33015079921407</v>
+        <v>6.452527045003777</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>16.85708697134771</v>
+        <v>6.034248430129985</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>14.17368287669305</v>
+        <v>4.769047797623514</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.0196</t>
+          <t>X ≈ -0.01976</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.485064970523013</v>
+        <v>1.218833994165877</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.881439128150028</v>
+        <v>4.228125875698858</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.473213987647227</v>
+        <v>3.835090851776208</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.607572001383296</v>
+        <v>8.583615774728706</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.087557639481417</v>
+        <v>6.20095724682843</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>7.370329466805316</v>
+        <v>8.347124822516818</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.6943269397265937</v>
+        <v>5.492222082029464</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.158486527904365</v>
+        <v>10.57411569213206</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7746383958891414</v>
+        <v>10.51599448064385</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.923300630338801</v>
+        <v>9.66980192479042</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.717666290484388</v>
+        <v>6.692395628969201</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.753735692619472</v>
+        <v>6.728613099005841</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.663032962851496</v>
+        <v>5.384816901428167</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.760203132062856</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01733</t>
+          <t>X ≈ -0.0175</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.997525629274378</v>
+        <v>2.212180393475357</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.457691509628631</v>
+        <v>4.866228162919775</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.592470673928133</v>
+        <v>8.734062138103013</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.706006340486148</v>
+        <v>8.86632907828492</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.189848554001799</v>
+        <v>8.331480525407407</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>9.001409314136026</v>
+        <v>10.33590808120191</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.874215245846123</v>
+        <v>8.548340656684744</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.434673392870387</v>
+        <v>8.937573774492215</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.375899965276929</v>
+        <v>10.5862283880585</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.067353013799519</v>
+        <v>9.740286007869699</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.350094707281528</v>
+        <v>9.538696182968209</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.384227044444408</v>
+        <v>9.575811765135164</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.454115337246897</v>
+        <v>8.304146977847907</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.676356673484491</v>
+        <v>5.968180340039254</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01505</t>
+          <t>X ≈ -0.01524</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3757649918326251</v>
+        <v>2.6112876295578</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.5220833601172</v>
+        <v>1.683936759879856</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.628027676067532</v>
+        <v>0.6118637500874797</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.381803182362461</v>
+        <v>4.133575803513246</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.030198688991938</v>
+        <v>1.562077977893452</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.588379804574565</v>
+        <v>3.895042352060884</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.62246109023917</v>
+        <v>5.169908612326161</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.138604708790226</v>
+        <v>2.667759137506074</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4.540304036780029</v>
+        <v>7.362757803611174</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.839030428587847</v>
+        <v>10.59313954640197</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.783725464766761</v>
+        <v>7.673284911513733</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.225035196357467</v>
+        <v>7.710072405882443</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.550478933784895</v>
+        <v>8.652722295417107</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.09271333696483453</v>
+        <v>7.520596178169768</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01278</t>
+          <t>X ≈ -0.01298</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.722545482260884</v>
+        <v>3.202234586198536</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.546443773900116</v>
+        <v>-0.2943397292604573</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.626785695951732</v>
+        <v>3.727055718503046</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8.237582003898076</v>
+        <v>1.964606048004782</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>8.796516828846045</v>
+        <v>3.322063147554111</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>9.09767243670511</v>
+        <v>2.356379756387916</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.634125895192163</v>
+        <v>1.009849221058843</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8.558456664100603</v>
+        <v>2.439425667140902</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.403714328159076</v>
+        <v>1.115141348665432</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.261233824985752</v>
+        <v>0.2667977481043309</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.350804603435193</v>
+        <v>3.224719263600768</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.385128100640436</v>
+        <v>1.362797769331962</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.674557075396208</v>
+        <v>0.3108892873874041</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>6.222810219937912</v>
+        <v>1.802866048143066</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.01051</t>
+          <t>X ≈ -0.01072</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.985048891153276</v>
+        <v>-0.8827245385795166</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.596178801084314</v>
+        <v>-4.607182037751301</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.995804865893362</v>
+        <v>-2.883389339839674</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.848553321307783</v>
+        <v>-4.345248178641235</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-10.43041289433592</v>
+        <v>-5.944210152335025</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-7.118879018036075</v>
+        <v>-4.588814524727191</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-9.220361113334036</v>
+        <v>-3.081922490612627</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.659267446809537</v>
+        <v>-3.548986045009251</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.733161786986912</v>
+        <v>-2.548956816620411</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.555647164533646</v>
+        <v>-0.2108715963756964</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-5.768042778386466</v>
+        <v>-1.47765989350313</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.724822501931662</v>
+        <v>-2.506439777629019</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.137013447686556</v>
+        <v>-3.99023576055292</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.889299892171962</v>
+        <v>-2.169662904186588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.008235</t>
+          <t>X ≈ -0.008459</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.276617111427292</v>
+        <v>2.28171118028434</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.518327896056029</v>
+        <v>-1.823120557218402</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.967206553609245</v>
+        <v>0.2838889773499744</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.507768525793082</v>
+        <v>2.417141438374458</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.119371988026245</v>
+        <v>2.382446164255228</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.319842913764326</v>
+        <v>0.1732324880728271</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>7.39106004821236</v>
+        <v>-1.414703223134637</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.72571273648429</v>
+        <v>-2.382687136321117</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.716886153000033</v>
+        <v>-1.942995138019668</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7649617651128509</v>
+        <v>-1.788652048387398</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.715625340600219</v>
+        <v>-1.49100422295372</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>5.852477916137516</v>
+        <v>2.5607693149448</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.229340777635599</v>
+        <v>1.137507604430972</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6250787332140817</v>
+        <v>-0.6460875807609483</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.005963</t>
+          <t>X ≈ -0.006197</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.236651771094969</v>
+        <v>2.89542007389776</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>6.228677874199995</v>
+        <v>0.3190604806177504</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.827986530201507</v>
+        <v>1.387470863978258</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.166502607914175</v>
+        <v>-0.9246677684499289</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>10.80996594314743</v>
+        <v>1.47023342530607</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.929994501690004</v>
+        <v>-0.1882668863401094</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.851301585876435</v>
+        <v>1.194814706535269</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5.185441576740637</v>
+        <v>1.707674080906266</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.427949173791035</v>
+        <v>-0.3102070241564903</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.120126133767606</v>
+        <v>-2.137894202519817</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4759311720678525</v>
+        <v>-0.8733843761078006</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.209027891016575</v>
+        <v>-2.308455817719036</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.693142119971483</v>
+        <v>-2.238542791850122</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.846708843836652</v>
+        <v>-1.03282519037765</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003691</t>
+          <t>X ≈ -0.003937</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>152</v>
+        <v>256</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.091190497703806</v>
+        <v>1.025765417015201</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.470577407477514</v>
+        <v>3.70328219342673</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.0923828567254219</v>
+        <v>3.696496869599095</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.012891393310355</v>
+        <v>-0.4515880136695785</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-8.168924746664246</v>
+        <v>-1.377709272364868</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.221683601157793</v>
+        <v>-3.807546095519911</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.683890930315016</v>
+        <v>-1.945263753569961</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-9.092465150459418</v>
+        <v>-4.36018119735224</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-8.503931838999812</v>
+        <v>-4.033117170012538</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-6.724812505302303</v>
+        <v>-2.933033176332586</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.928041632224087</v>
+        <v>-1.967451403509656</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-8.208179121081642</v>
+        <v>-2.713971118498144</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.345201229177896</v>
+        <v>-2.353309936453002</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.467183996371972</v>
+        <v>0.6062679468772458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001419</t>
+          <t>X ≈ -0.001677</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>165</v>
+        <v>280</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.231007567896633</v>
+        <v>0.7240294208440829</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>8.272556306955565</v>
+        <v>1.612316352166225</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.779488524307389</v>
+        <v>-3.759814661368878</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.976541071095923</v>
+        <v>-0.7851807194519367</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.64825349154971</v>
+        <v>0.8123671369581018</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.087150633814318</v>
+        <v>-2.80459550190907</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1509169200437839</v>
+        <v>-1.110228679761988</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.801229611180865</v>
+        <v>-1.931849182585999</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.495054574844403</v>
+        <v>-2.706710571877693</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-6.368724650024959</v>
+        <v>-4.982332239606421</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.361500152325405</v>
+        <v>-5.545002336855887</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.327763425776858</v>
+        <v>-5.512524694168803</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.9340367695753</v>
+        <v>-4.149237081170057</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.081219084091266</v>
+        <v>-3.210696338836961</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.000853</t>
+          <t>X ≈ 0.0005845</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.123795569539801</v>
+        <v>0.4274334116754517</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.755870170834982</v>
+        <v>3.858053312916624</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.356038192449752</v>
+        <v>6.173474388357945</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7.23134111450986</v>
+        <v>8.629864794355768</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.707302938631848</v>
+        <v>6.160817120913784</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.973728381255036</v>
+        <v>2.975400523443803</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.934067074724311</v>
+        <v>5.993258371482646</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.471558185567993</v>
+        <v>7.471570204848881</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.4114677287502602</v>
+        <v>6.637898261863334</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.565860297655057</v>
+        <v>6.181813255074616</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.115379261996623</v>
+        <v>5.592750692002312</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4.648086834878384</v>
+        <v>5.630440688804221</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.98041772755014</v>
+        <v>5.602952816512058</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.983943823176901</v>
+        <v>6.999142460495833</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.003125</t>
+          <t>X ≈ 0.002845</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>136</v>
+        <v>257</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.970913071346644</v>
+        <v>-2.863305304438214</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-7.397687045244773</v>
+        <v>-0.6047494972673846</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.328470553513071</v>
+        <v>-0.2265686633973445</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.543902252405637</v>
+        <v>-0.09588334242535268</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.08451408905421</v>
+        <v>-1.794401563416933</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.05962062732754</v>
+        <v>-0.3341850498113246</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.610540808681584</v>
+        <v>-0.8059830957080081</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.417038569813514</v>
+        <v>-2.436858001093078</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-6.683564847108777</v>
+        <v>-3.066832575784929</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.596268343077867</v>
+        <v>-1.198140544605707</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.532938712860513</v>
+        <v>-1.01331129731043</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-7.700158796229303</v>
+        <v>-3.699033848692757</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-7.391577866108641</v>
+        <v>-4.11985232732134</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-10.09102300565989</v>
+        <v>-5.841324465574118</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.005397</t>
+          <t>X ≈ 0.005106</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-11.60034949087823</v>
+        <v>-5.562742335974619</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-9.736543229855307</v>
+        <v>-5.161871132415968</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-13.62509948160664</v>
+        <v>-6.365832167046818</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-8.590478182333158</v>
+        <v>-1.736135765317094</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.532060787752101</v>
+        <v>0.57524979802659</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.1451838498825</v>
+        <v>0.4522056750366303</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.93335636291625</v>
+        <v>-0.4358960505020022</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.113061794447589</v>
+        <v>0.7197913755839167</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.841677117947292</v>
+        <v>-0.1584335341043328</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.392394734887404</v>
+        <v>0.4310149311251834</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.478617565849333</v>
+        <v>-2.835699489913708</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.809711840965228</v>
+        <v>-1.351960097962412</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.895025450708857</v>
+        <v>1.727178909841463</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.331926455814838</v>
+        <v>1.36190319277889</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00767</t>
+          <t>X ≈ 0.007366</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.402197194236919</v>
+        <v>0.6783363337281472</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.298709606729197</v>
+        <v>1.174530733720907</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.662997387674871</v>
+        <v>-0.9021722380294221</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5289915593717893</v>
+        <v>-2.037231110010538</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.7674374039630365</v>
+        <v>-5.099590080684145</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.037154078187676</v>
+        <v>-3.960393920505325</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.9542404137461915</v>
+        <v>-5.734196582071334</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.2674964988972661</v>
+        <v>-5.782254283683436</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.596186584950651</v>
+        <v>-3.73353179885595</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.695787914401514</v>
+        <v>-1.207923169025527</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.6378881117042781</v>
+        <v>1.119021242334583</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.119663884081618</v>
+        <v>0.7314584664197668</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4803103895641385</v>
+        <v>-0.5325742434336718</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.111522114394305</v>
+        <v>0.9589841916029798</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.009943</t>
+          <t>X ≈ 0.009628</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>112</v>
+        <v>215</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-5.611746079576726</v>
+        <v>1.921129227283721</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.679026345321994</v>
+        <v>3.55669465513256</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5005532232703587</v>
+        <v>2.238764643708286</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.153617144328258</v>
+        <v>0.5148846825860289</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.02544743054906462</v>
+        <v>1.37365111297364</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.051259574927101</v>
+        <v>1.676283239240419</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.911802355350751</v>
+        <v>4.381507004124302</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.658904670854959</v>
+        <v>7.176238504070518</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>4.597904784672657</v>
+        <v>6.650140068477924</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>4.404872434938753</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.757311989612816</v>
+        <v>2.804822439469156</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.577409432672582</v>
+        <v>3.304316870894411</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.050011964584819</v>
+        <v>4.279514854790243</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.299733296861064</v>
+        <v>5.435483063156319</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.01222</t>
+          <t>X ≈ 0.01189</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.107307262405698</v>
+        <v>0.7070746643524686</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.587857013553972</v>
+        <v>2.818816158889618</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.983276118714706</v>
+        <v>0.3012153287671993</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.880005616739879</v>
+        <v>-2.227535884258145</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-9.530667946905609</v>
+        <v>-5.967667462772859</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.126070702045546</v>
+        <v>-4.07630882749671</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.241732254369431</v>
+        <v>-6.296575674058381</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-5.677987818099382</v>
+        <v>-7.021000645289071</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-6.769915539333233</v>
+        <v>-12.42957638469954</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-8.650968559412711</v>
+        <v>-12.74473582274063</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-10.91757755383332</v>
+        <v>-11.87991826442322</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-4.697627386178695</v>
+        <v>-10.77602139549042</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.117881997123575</v>
+        <v>-11.19617224880383</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.80630499474416</v>
+        <v>-13.64423339002115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01449</t>
+          <t>X ≈ 0.01415</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-5.796906000964405</v>
+        <v>1.739214628646721</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.103360907800578</v>
+        <v>-2.459201598063984</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1561557407181908</v>
+        <v>1.044839831579289</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.948035567799053</v>
+        <v>-2.725603566215085</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.414683290277544</v>
+        <v>0.000563076267170004</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.722726548813505</v>
+        <v>4.870708479969601</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.448444706756732</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>4.327781291728193</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5568571200892478</v>
+        <v>8.841962533898197</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.259684361549489</v>
+        <v>7.338448966326553</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.388264370565253</v>
+        <v>6.480153036824483</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.422647527910748</v>
+        <v>7.821720731663468</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.002392916965782</v>
+        <v>8.708759420833715</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.918780915908769</v>
+        <v>9.588089842302075</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01675</t>
+          <t>X ≈ 0.01641</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.286116095538091</v>
+        <v>-1.387566218157197</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-3.41250004639442</v>
+        <v>-2.997034373892575</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.451767394785385</v>
+        <v>-1.929518582577217</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.777868635793538</v>
+        <v>-5.082686624255381</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-6.943714022263507</v>
+        <v>-3.421051922490193</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.185949250273254</v>
+        <v>2.01182098914019</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-4.010408994942793</v>
+        <v>1.200078693684837</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3680033526284063</v>
+        <v>2.938892402839237</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.168729266207968</v>
+        <v>-0.06326622427173589</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.09073458985999849</v>
+        <v>-1.648479138248696</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.995570306638349</v>
+        <v>0.3527020564322854</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.449498590810819</v>
+        <v>-2.55409626180063</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.609698853038878</v>
+        <v>-1.503658879819874</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.119694157917863</v>
+        <v>-4.954393817828674</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01903</t>
+          <t>X ≈ 0.01867</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.296182745595885</v>
+        <v>-4.399547560816366</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.93957682305156</v>
+        <v>-10.34187051344436</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7227086762153618</v>
+        <v>-7.352370584376651</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.138084667311155</v>
+        <v>-4.392849979913862</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>11.99058102164857</v>
+        <v>-0.6575867273843841</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.879959253216015</v>
+        <v>-5.562059275421426</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.525529181037392</v>
+        <v>-10.87275043796782</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.992712579818892</v>
+        <v>-15.1493428912784</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-4.280127560340816</v>
+        <v>-10.44842028589638</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.130252745368743</v>
+        <v>-11.29833908222627</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-7.221798522516593</v>
+        <v>-8.645897383343531</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-7.187415365171084</v>
+        <v>-7.65913827860728</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.834085070455664</v>
+        <v>-5.222146274777884</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-9.244741096669884</v>
+        <v>-4.996410624551238</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.02131</t>
+          <t>X ≈ 0.02093</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.142086968858585</v>
+        <v>-0.6736871148717327</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.354447526285227</v>
+        <v>4.944042454715039</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.851231991122134</v>
+        <v>2.139632515743173</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-5.720978858514712</v>
+        <v>1.065038382223058</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.848708034521266</v>
+        <v>5.346025937561173</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5565527304657749</v>
+        <v>-3.995154249671252</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-6.046691853143457</v>
+        <v>-7.694322440262717</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-9.21657795462766</v>
+        <v>-11.77584891537472</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-6.574875138107259</v>
+        <v>-9.427192517680666</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.722297620432492</v>
+        <v>-9.072292036902056</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.927050944750029</v>
+        <v>-9.276993195162284</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.189965084701932</v>
+        <v>-4.423337934373194</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.312922398349542</v>
+        <v>-2.433850233469741</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3422043393321204</v>
+        <v>-1.003295306134838</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.02357</t>
+          <t>X ≈ 0.02319</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4101049868766395</v>
+        <v>-9.271039487324437</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.144988066825803</v>
+        <v>-3.474818172980918</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.583213973104186</v>
+        <v>-10.04242906390876</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.452960840496601</v>
+        <v>-7.443068117851261</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1.341951277764494</v>
+        <v>-1.808518164774128</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.721326164874554</v>
+        <v>-0.3612865931706253</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.254142766093089</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>5.193142879910752</v>
+        <v>1.579798408988964</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.42635102821616</v>
+        <v>3.199015415128237</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.304931037231924</v>
+        <v>2.994314256868051</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>12.50598086124401</v>
+        <v>7.966964014161654</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>5.077677358379105</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>10.25211424924208</v>
+        <v>4.068845107371075</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.02584</t>
+          <t>X ≈ 0.02545</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.506561679789989</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.39072621888856</v>
+        <v>-4.09210212359816</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>-6.272587794067533</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.773229635693781</v>
+        <v>-0.7852197933362675</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6223344365211645</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11.10367892976591</v>
+        <v>-1.026135316796896</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>-4.682274247491662</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.694618956569201</v>
+        <v>0.2077999658644885</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9378095010416274</v>
+        <v>-1.638896476372558</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>-6.060243844130987</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-4.815447710184564</v>
+        <v>-8.016281135750162</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.985980988853157</v>
+        <v>-9.996410624551324</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02812</t>
+          <t>X ≈ 0.02771</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>-4.564249363867681</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.500119360229178</v>
+        <v>-6.570206841686549</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.630372492836685</v>
+        <v>-4.356648364764887</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.09195127776448</v>
+        <v>1.355062082139447</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>21.38939321548014</v>
+        <v>9.985769445107877</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.30465949820789</v>
+        <v>1.567725752508331</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.83747609942639</v>
+        <v>9.433990442054927</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>5.206341618865494</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.07364897178383245</v>
+        <v>4.356422822535656</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.244019138755988</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.664273749700889</v>
+        <v>1.682615629984014</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-8.414552417424602</v>
+        <v>-4.341648719789418</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.0304</t>
+          <t>X ≈ 0.02997</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>8.125144575526257</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>20.89498806682573</v>
+        <v>0.4533524218563372</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>20.50011936022918</v>
+        <v>-2.971721993201726</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>45.63037249283668</v>
+        <v>3.219109210992755</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>20.09195127776447</v>
+        <v>-6.410089433012068</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-3.08241237307395</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>20.30465949820789</v>
+        <v>-0.1368197020370232</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.337476099426389</v>
+        <v>-6.664494406429846</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-12.78608262355868</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-16.66630445019162</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-13.84070257814878</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>-13.80632442579346</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-11.19617224880379</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>-4.909830537971217</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.03266</t>
+          <t>X ≈ 0.03223</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>15.89498806682581</v>
+        <v>5.907897876401847</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-4.499880639770787</v>
+        <v>10.51312649164678</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>5.64335163523517</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-14.90804872223547</v>
+        <v>0.105062082139483</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-14.61060678451983</v>
+        <v>-4.597563888225501</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-14.69534050179211</v>
+        <v>-9.682274247491669</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-5.162523900573575</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-15.22352378675591</v>
+        <v>-10.21032504780118</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-16.07364897178384</v>
+        <v>-16.06024384413101</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-16.27840229610142</v>
+        <v>-11.2649450023912</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-16.24401913875599</v>
+        <v>-11.23056685003588</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-16.66427374970089</v>
+        <v>-16.65071770334932</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-16.4145524174246</v>
+        <v>-11.42498205312279</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-20 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-20 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,1561 +2210,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.03209</t>
+          <t>X &gt; -0.0322</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2198</v>
+        <v>4073</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.838109522024034</v>
+        <v>0.03988671053271275</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.5659919694718738</v>
+        <v>0.05722468178737472</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.233092980968649</v>
+        <v>-0.1039156239261914</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2129496253230627</v>
+        <v>-0.08283009388559748</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.007867234032218562</v>
+        <v>-0.1668634445631483</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.003253175804438513</v>
+        <v>-0.1991321313031378</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1184651294522183</v>
+        <v>-0.1479605220014406</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.09664475473081069</v>
+        <v>-0.1848908196921926</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.723523786755905</v>
+        <v>-0.1833510409350367</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.7554671536020194</v>
+        <v>-0.185826380309571</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1306886129894878</v>
+        <v>-0.2050823919888458</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1076555023923476</v>
+        <v>-0.2305668500358706</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.3161719074159848</v>
+        <v>-0.1951457838598429</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.04586614490479235</v>
+        <v>-0.1765165485806435</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02982</t>
+          <t>X &gt; -0.02993</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2182</v>
+        <v>4047</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.9173761913840224</v>
+        <v>-0.01786184334223861</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.6315201598652749</v>
+        <v>0.03453005181447821</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.2549080620743</v>
+        <v>-0.02654822496239007</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.06364488771784949</v>
+        <v>-0.006143065282479654</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1548494534969223</v>
+        <v>-0.1365552748625234</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1524449189505575</v>
+        <v>-0.1955910152291693</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.01646187698191426</v>
+        <v>-0.1435470644625241</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1510822529763516</v>
+        <v>-0.1283707718606593</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8279193911515179</v>
+        <v>-0.1757742087093348</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.8080812062160732</v>
+        <v>-0.1234381171500232</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.08606656836744264</v>
+        <v>-0.1661795702924351</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1542755490123966</v>
+        <v>-0.216736274585152</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.3215256089798189</v>
+        <v>-0.1289785729145052</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.00157957157631472</v>
+        <v>-0.1363732070639472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02755</t>
+          <t>X &gt; -0.02767</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2158</v>
+        <v>4007</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.7613367035817973</v>
+        <v>0.08127302419202209</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.5929971457435457</v>
+        <v>0.07560128520998433</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.31134089855086</v>
+        <v>0.01785521240336863</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.02039097712502524</v>
+        <v>0.01228367407009046</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1945551917364128</v>
+        <v>-0.1140614238366524</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.01051432034969224</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.207527213286518</v>
+        <v>0.001333126698703779</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.04915046235056764</v>
+        <v>-0.0534046904311225</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.7790793423114692</v>
+        <v>-0.1255792850892874</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.7495748977097705</v>
+        <v>-0.08916431284205117</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1567828890837717</v>
+        <v>-0.1053440048849694</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.08661173134857592</v>
+        <v>-0.1816768525302663</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4454992933746027</v>
+        <v>-0.06389135604390361</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1192752007403612</v>
+        <v>-0.0985533034347057</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02528</t>
+          <t>X &gt; -0.02541</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2135</v>
+        <v>3958</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.7193953696964286</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.6720366879617075</v>
+        <v>0.06406916103657778</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.34714827171851</v>
+        <v>0.01048098900128025</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.04921648427681902</v>
+        <v>0.003230667493205885</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2606876759954204</v>
+        <v>-0.1180284144574841</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.07789650414599691</v>
+        <v>-0.1346289411755421</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.09661835748791958</v>
+        <v>-0.07949997258621266</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.1578466320983978</v>
+        <v>-0.154388299956473</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.8014367488523106</v>
+        <v>-0.2014933546394104</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8092596409462161</v>
+        <v>-0.2046153736615466</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1558513304778941</v>
+        <v>-0.1427536365744899</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1841220868140141</v>
+        <v>-0.2204658399348673</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2645652016099689</v>
+        <v>-0.07077327293756497</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.02110979447378725</v>
+        <v>-0.03286482219804299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.023</t>
+          <t>X &gt; -0.02315</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2112</v>
+        <v>3920</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5821594150660445</v>
+        <v>0.1252370332846198</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4222923864320265</v>
+        <v>0.1805326678565535</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.194875918335512</v>
+        <v>0.1302722560833089</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.06852169019267507</v>
+        <v>0.1217231365074056</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2338277590626916</v>
+        <v>-0.04637594280328727</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.0522695147985317</v>
+        <v>-0.04053741164705826</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1250753772249027</v>
+        <v>-0.06042550799583779</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.07978158378873701</v>
+        <v>-0.1060418214872314</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.8715843354787154</v>
+        <v>-0.203955621049559</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.9175467958141184</v>
+        <v>-0.2243620908180617</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.01298843237540126</v>
+        <v>-0.1854140311956911</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.2837542380937421</v>
+        <v>-0.238725952534601</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1270182521921583</v>
+        <v>-0.1345228550962858</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2119009022730864</v>
+        <v>-0.0984514408778594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.02073</t>
+          <t>X &gt; -0.02089</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2078</v>
+        <v>3853</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.7428387998262878</v>
+        <v>0.07987031193849248</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6981021443066666</v>
+        <v>0.1381695452245921</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.620801944953165</v>
+        <v>-0.03552775265963959</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.09899410985045876</v>
+        <v>0.08290638542929685</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3974921003544907</v>
+        <v>-0.1305671255249692</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.3619269957536204</v>
+        <v>-0.2075094981710777</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.180450972493361</v>
+        <v>-0.2263156982688415</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4292226031204578</v>
+        <v>-0.2128308415245428</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.088908402140532</v>
+        <v>-0.285493528879428</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.169802817937679</v>
+        <v>-0.343365441227192</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.268786911486032</v>
+        <v>-0.326148321893271</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5228652926021411</v>
+        <v>-0.3550804687129201</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1467172321443684</v>
+        <v>-0.2417919119637091</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.4472761902831195</v>
+        <v>-0.1830926163202591</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01846</t>
+          <t>X &gt; -0.01863</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2028</v>
+        <v>3745</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.896386723158372</v>
+        <v>0.04702436329214521</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8110099666058943</v>
+        <v>0.02022153889849676</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.845013383133647</v>
+        <v>-0.1471503986620561</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2889982052950799</v>
+        <v>-0.1622409080404879</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4341057527173078</v>
+        <v>-0.3131584825915041</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5525644825031009</v>
+        <v>-0.454211903146863</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1677814466739989</v>
+        <v>-0.3912294713722346</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.3619330586238263</v>
+        <v>-0.5239096734697881</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.134853836016994</v>
+        <v>-0.5969917144678121</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.246062764887292</v>
+        <v>-0.632129680353998</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3670722468403298</v>
+        <v>-0.5285522595950454</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5789945082141159</v>
+        <v>-0.5593632204655563</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.08467788967131185</v>
+        <v>-0.4040545960348183</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5467023188052735</v>
+        <v>-0.296811158596725</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01619</t>
+          <t>X &gt; -0.01637</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1962</v>
+        <v>3628</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7920670657660906</v>
+        <v>-0.02280012830968303</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.9546054291091934</v>
+        <v>-0.136058167554225</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.162482265787091</v>
+        <v>-0.4335621590814398</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4570258811470538</v>
+        <v>-0.4534048243580386</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6905690474387498</v>
+        <v>-0.59194094233127</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.873951980249366</v>
+        <v>-0.8021843502716735</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2701116106425658</v>
+        <v>-0.6795232158547719</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.5569259361970182</v>
+        <v>-0.8290346909481556</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.35387001893514</v>
+        <v>-0.9576413153486243</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.592997240622935</v>
+        <v>-0.9666315093292397</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6266711352052852</v>
+        <v>-0.8532126972411049</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.8468704625849028</v>
+        <v>-0.8862142329559859</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2709981511272801</v>
+        <v>-0.6848868959643326</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6551232635000375</v>
+        <v>-0.4988519538945297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01392</t>
+          <t>X &gt; -0.01411</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1875</v>
+        <v>3481</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8462544732386661</v>
+        <v>-0.134035664192055</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.8354744531104288</v>
+        <v>-0.2129151782789691</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.187280958750087</v>
+        <v>-0.4777097053749841</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7279475496938872</v>
+        <v>-0.6471095506714732</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.628410232070685</v>
+        <v>-0.6829035339063978</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8872025292006782</v>
+        <v>-1.000544685015385</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.3579269839634733</v>
+        <v>-0.9265403025375036</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.5299360411486944</v>
+        <v>-0.9767016523910783</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.627359695120326</v>
+        <v>-1.309005483830987</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.891443324474309</v>
+        <v>-1.454791907258702</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9241135374439864</v>
+        <v>-1.213280249233911</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.943006885159825</v>
+        <v>-1.249228922961521</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5875146878671984</v>
+        <v>-1.079207077272315</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.6812190840912677</v>
+        <v>-0.8375071895777921</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01164</t>
+          <t>X &gt; -0.01185</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1784</v>
+        <v>3323</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.181322183973236</v>
+        <v>-0.2926666300547396</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.6971907041239547</v>
+        <v>-0.2090436528335573</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.43284153362557</v>
+        <v>-0.6776353559836963</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.185269965263885</v>
+        <v>-0.7712898289112715</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.109166040671248</v>
+        <v>-0.8733292744031687</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.396520702909996</v>
+        <v>-1.160157703896438</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6125664525751162</v>
+        <v>-1.018610583827972</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9935255793648849</v>
+        <v>-1.139129614017932</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.088025466487153</v>
+        <v>-1.424267355493463</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.154276071447889</v>
+        <v>-1.536649013953671</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.295199608531433</v>
+        <v>-1.42429557364796</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.316807492619368</v>
+        <v>-1.373423992893017</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.7539096040426259</v>
+        <v>-1.145302540894413</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.033386498142086</v>
+        <v>-0.963050063956338</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009372</t>
+          <t>X &gt; -0.009589</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1685</v>
+        <v>3135</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.134100258744255</v>
+        <v>-0.257281977167132</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4681106913055118</v>
+        <v>0.05470435876596724</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.282257931314291</v>
+        <v>-0.5453604759310906</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.087545898647647</v>
+        <v>-0.5569663297887075</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5615082136606873</v>
+        <v>-0.5692381723134758</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.06031092653167</v>
+        <v>-0.954547661690313</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1068265882337869</v>
+        <v>-0.8948776847927178</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7193959384883115</v>
+        <v>-0.9946150975820913</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.815106477923663</v>
+        <v>-1.356821863087767</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.013186612566294</v>
+        <v>-1.616153369457543</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.032403481637871</v>
+        <v>-1.421095416667811</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.11657396981704</v>
+        <v>-1.305479186663227</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.5551397046237838</v>
+        <v>-0.9746972951860258</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8655909930922547</v>
+        <v>-0.8906917819903768</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.007099</t>
+          <t>X &gt; -0.007328</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1590</v>
+        <v>2936</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.397633686521807</v>
+        <v>-0.4293731346374372</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3456134369336255</v>
+        <v>0.1819820012322069</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.18158490042245</v>
+        <v>-0.6015664163952934</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.362108710170844</v>
+        <v>-0.7585492473174753</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9606803011828617</v>
+        <v>-0.769301245534578</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.381766659127976</v>
+        <v>-1.03098780126895</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5548135256315163</v>
+        <v>-0.859644278072679</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9252357649803926</v>
+        <v>-0.9005325581716406</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.145634339519731</v>
+        <v>-1.317091453785508</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.179176609974796</v>
+        <v>-1.604461531205835</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.316090738312475</v>
+        <v>-1.41635704730443</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.532963862374075</v>
+        <v>-1.567530771070587</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6617596076518666</v>
+        <v>-1.117861046897119</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8799612224560462</v>
+        <v>-0.9072708814606329</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004827</t>
+          <t>X &gt; -0.005067</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1479</v>
+        <v>2732</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.820490810115764</v>
+        <v>-0.6776373420097599</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.839018667180973</v>
+        <v>0.1717462729032775</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.782708922599106</v>
+        <v>-0.7500889658814671</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.777034914570734</v>
+        <v>-0.7461450824891429</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.844075658262426</v>
+        <v>-0.9365285782035002</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.780418105274549</v>
+        <v>-1.09391425318897</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.8854955928238013</v>
+        <v>-1.013051903570492</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.383846437685619</v>
+        <v>-1.095288837224317</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.48888502915969</v>
+        <v>-1.392276089087233</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.258659100075533</v>
+        <v>-1.564629809043296</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.450583254913035</v>
+        <v>-1.456901126705645</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.888853709991636</v>
+        <v>-1.512205474761551</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9885980740252194</v>
+        <v>-1.034179101080717</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.309751876518582</v>
+        <v>-0.8978956695209988</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.002555</t>
+          <t>X &gt; -0.002807</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1327</v>
+        <v>2476</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.268550763988088</v>
+        <v>-0.8537565287264002</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7666773495283223</v>
+        <v>-0.1933882972316212</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.112033678030386</v>
+        <v>-1.20983289717509</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.406386696960773</v>
+        <v>-0.7766000944511049</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.119601610457543</v>
+        <v>-0.8909137729913397</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.157153331066375</v>
+        <v>-0.8133448866151625</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4504118766981975</v>
+        <v>-0.9166681258645681</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5008697652352652</v>
+        <v>-0.7577232297151184</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.799896999697971</v>
+        <v>-1.119232746309812</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.747087647479852</v>
+        <v>-1.423147069937457</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.8231728002398739</v>
+        <v>-1.404114022157238</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.165012366746957</v>
+        <v>-1.387951837929343</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4895749545201653</v>
+        <v>-0.8977907756141263</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.17717487409378</v>
+        <v>-1.053415009504015</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002829</t>
+          <t>X &gt; -0.000546</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1162</v>
+        <v>2196</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.049469115761731</v>
+        <v>-1.054931422114258</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.050217412626289</v>
+        <v>-0.4236238627286113</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.301250502784519</v>
+        <v>-0.8846986103015624</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.886750794834562</v>
+        <v>-0.7755060256896087</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.654624064701252</v>
+        <v>-1.108089845298196</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8831003577846133</v>
+        <v>-0.5594513655394451</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.492939129579419</v>
+        <v>-0.891988273819365</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.827759952075759</v>
+        <v>-0.6080168240667447</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.701187016996464</v>
+        <v>-0.9168220945980607</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.090831102368028</v>
+        <v>-0.969334753221915</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.1787459387130994</v>
+        <v>-0.8761319055289931</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5739160459724815</v>
+        <v>-0.8620500165508957</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.0004732337937554121</v>
+        <v>-0.483216565433942</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9068071506431892</v>
+        <v>-0.7783518163285876</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001989</t>
+          <t>X &gt; 0.001715</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1029</v>
+        <v>1939</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.169113995885652</v>
+        <v>-1.251407833813047</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.800664107087272</v>
+        <v>-0.9911282640389842</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.161716388563093</v>
+        <v>-1.820206841686556</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.065279681076362</v>
+        <v>-2.022117836288714</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.347662248805534</v>
+        <v>-2.071529293630569</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.7421348309414952</v>
+        <v>-1.02796964066512</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.065137210407798</v>
+        <v>-1.804576405765012</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.383454133131757</v>
+        <v>-1.678905873283519</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.97425123583448</v>
+        <v>-1.918143977842306</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.563464684683936</v>
+        <v>-1.917166129257097</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.9922723251993872</v>
+        <v>-1.733534085810355</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.248868799279748</v>
+        <v>-1.722581275589718</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.2565067594096249</v>
+        <v>-1.289892961081243</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.409693330932861</v>
+        <v>-1.809200722539977</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.004261</t>
+          <t>X &gt; 0.003975</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>893</v>
+        <v>1682</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.437820967595961</v>
+        <v>-1.005119100191962</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.100557590189823</v>
+        <v>-1.050164734348328</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.83172919210935</v>
+        <v>-2.063705659653458</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.144683186450628</v>
+        <v>-2.316435472984843</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.235442931589617</v>
+        <v>-2.113872829103158</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5414874980092392</v>
+        <v>-1.133975966378223</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.6774833589349711</v>
+        <v>-1.95715576407931</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.9214524720021799</v>
+        <v>-1.563095114159225</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.257043339828535</v>
+        <v>-1.7426309162066</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.101581932677696</v>
+        <v>-2.027029134759715</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3007486648165028</v>
+        <v>-1.843580017228</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2663655074710718</v>
+        <v>-1.420590603005003</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.8301334091358044</v>
+        <v>-0.8574913218876077</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.0875647354537179</v>
+        <v>-1.193115227914667</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.006534</t>
+          <t>X &gt; 0.006236</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>751</v>
+        <v>1438</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7053588500112937</v>
+        <v>-0.2317810824374646</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6567360711052714</v>
+        <v>-0.3524899352325335</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.979986740566581</v>
+        <v>-1.333720355200064</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.114985597348998</v>
+        <v>-2.414900791949329</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.990276838946372</v>
+        <v>-2.570163455681502</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4273398522489202</v>
+        <v>-1.403119443781023</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.4400213528559433</v>
+        <v>-2.215283281543051</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.306140921850208</v>
+        <v>-1.950455547745683</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.032034425053787</v>
+        <v>-2.011437704268459</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.95130854625193</v>
+        <v>-2.444110325354934</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.8262746365269535</v>
+        <v>-1.67523707471387</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6589127557772656</v>
+        <v>-1.432235834736851</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.2506198673203883</v>
+        <v>-1.296058454392401</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3559638688227409</v>
+        <v>-1.626651037823727</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.008806</t>
+          <t>X &gt; 0.008497</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>619</v>
+        <v>1201</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.368036390949527</v>
+        <v>-0.4113796066932949</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.286976506443153</v>
+        <v>-0.6538254044598233</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.970089979545385</v>
+        <v>-1.418880141852391</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.678806251124676</v>
+        <v>-2.489428447752402</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.251043891317615</v>
+        <v>-2.071017652079817</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7396390425843506</v>
+        <v>-0.8984782689403374</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.7373437328098831</v>
+        <v>-1.520876576942555</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.527628908651153</v>
+        <v>-1.194305422502346</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.91173057189323</v>
+        <v>-1.671607312580498</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.792550425741837</v>
+        <v>-2.688054002332507</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.8664475303502073</v>
+        <v>-2.22664358690411</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.3474117074151124</v>
+        <v>-1.859209647704482</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2016390128193066</v>
+        <v>-1.446721033907153</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1948432090239578</v>
+        <v>-2.136888797502436</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.01108</t>
+          <t>X &gt; 0.01076</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>507</v>
+        <v>986</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4305699508583061</v>
+        <v>-0.9199895451365663</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.75855524026084</v>
+        <v>-1.571940833275605</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.515628671266889</v>
+        <v>-2.216439603206901</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.794824357557026</v>
+        <v>-3.144527152643647</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.742694391526832</v>
+        <v>-2.822137108962671</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.356168914697342</v>
+        <v>-1.45991206636311</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.427095925855227</v>
+        <v>-2.80790747950784</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.894279324636727</v>
+        <v>-3.019525447059308</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.34975652837327</v>
+        <v>-3.486187116766665</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.424733784407117</v>
+        <v>-4.234686034800383</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.446055156061966</v>
+        <v>-3.323768531802962</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.214433339939418</v>
+        <v>-2.985130744559207</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.6484946569987216</v>
+        <v>-2.69534244979959</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.187727959830909</v>
+        <v>-3.788065217422954</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.01335</t>
+          <t>X &gt; 0.01302</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>410</v>
+        <v>799</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7944091939963869</v>
+        <v>-1.300791806931869</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.550267407626784</v>
+        <v>-2.59956481016534</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.404990128821915</v>
+        <v>-2.805677991541266</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.301500986482054</v>
+        <v>-3.359142130350889</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.136759184522596</v>
+        <v>-2.085949153815612</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.464265321105195</v>
+        <v>-0.8475638882254657</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.524608794475036</v>
+        <v>-1.991410668017288</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.235694632280925</v>
+        <v>-2.083009975133187</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.540596957487615</v>
+        <v>-1.393053458314292</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.9516977522716417</v>
+        <v>-2.242972254644151</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.7947684356058957</v>
+        <v>-1.321265402891825</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3903606021706167</v>
+        <v>-1.161730804979555</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.408896982006425</v>
+        <v>-0.7057865393943388</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8047963198636197</v>
+        <v>-1.481302453623378</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01562</t>
+          <t>X &gt; 0.01528</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>335</v>
+        <v>646</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.325552777712879</v>
+        <v>-2.02079333114785</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.426440504602802</v>
+        <v>-2.632808728820919</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.202261592151778</v>
+        <v>-3.717642739122454</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.476770364306184</v>
+        <v>-3.509190737646215</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.931858246045017</v>
+        <v>-2.580123103045736</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.177770963624312</v>
+        <v>-2.201891554376935</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.05354945701599</v>
+        <v>-3.753481677832191</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.326703005051222</v>
+        <v>-3.601355275179309</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.984717816606661</v>
+        <v>-3.817136193311981</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.342305688201748</v>
+        <v>-4.512256228031944</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.4575067737133622</v>
+        <v>-3.168969770193058</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.915660929800772</v>
+        <v>-3.289390379447639</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.843378227312833</v>
+        <v>-2.935547424711515</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.981716596529083</v>
+        <v>-4.103000628974144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01789</t>
+          <t>X &gt; 0.01754</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>262</v>
+        <v>510</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.2207110474827019</v>
+        <v>-2.189653894612022</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.8730727696761349</v>
+        <v>-2.535681890135152</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-4.689994708211891</v>
+        <v>-4.194475847534513</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.278372754311611</v>
+        <v>-3.089591834550433</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5354251480910079</v>
+        <v>-2.355875417860553</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.17549228070304</v>
+        <v>-3.325548232648167</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.786943555227225</v>
+        <v>-5.074431110236731</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.872447564695747</v>
+        <v>-5.345421322650921</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.933447450878049</v>
+        <v>-4.818168185056052</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.020213857280019</v>
+        <v>-5.275930118640815</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.698249624345699</v>
+        <v>-4.108082257293155</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.04554585631324</v>
+        <v>-3.485468810820187</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.08412107794517</v>
+        <v>-3.317384370015951</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.124476081546739</v>
+        <v>-3.875962445279612</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.02017</t>
+          <t>X &gt; 0.0198</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>209</v>
+        <v>405</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.573547325723041</v>
+        <v>-1.616718499670156</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.9189115118018449</v>
+        <v>-0.5118552100179414</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.696052888574648</v>
+        <v>-3.375762397242113</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.651924157881027</v>
+        <v>-2.751710093159922</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.711876473431666</v>
+        <v>-2.79617248576178</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.457496736672944</v>
+        <v>-2.745712036373618</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.585292654902155</v>
+        <v>-3.571163136380527</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.574007154162125</v>
+        <v>-2.803663878932689</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.591944839387494</v>
+        <v>-3.358473195949301</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.485132225372354</v>
+        <v>-3.714564831785324</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.2975410520822734</v>
+        <v>-2.931611669057865</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7416267942583801</v>
+        <v>-2.403406356208713</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.640350304724812</v>
+        <v>-2.823557209522122</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.826035671013116</v>
+        <v>-3.585475880283255</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.02244</t>
+          <t>X &gt; 0.02206</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>172</v>
+        <v>322</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.157724470487693</v>
+        <v>-1.859798018111988</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.03524449131376883</v>
+        <v>-1.918189080119923</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.662671337445246</v>
+        <v>-4.797432514564399</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.206836809488898</v>
+        <v>-3.735530352342494</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.866420738008202</v>
+        <v>-2.423650844747208</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6255730599316465</v>
+        <v>-2.508361204013376</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.07003423896127003</v>
+        <v>-0.4909577981106708</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.735151693732661</v>
+        <v>-1.794175979478169</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.003881529923376</v>
+        <v>-2.33353576959685</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.6983418899450911</v>
+        <v>-1.29600090301232</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.4300656503838951</v>
+        <v>-1.882740763079362</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8503202613287968</v>
+        <v>-2.924009628815128</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.507575673238549</v>
+        <v>-4.251069009644496</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.02471</t>
+          <t>X &gt; 0.02432</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.151722970112601</v>
+        <v>0.6311171644863975</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.8792054815613355</v>
+        <v>-1.395006687913529</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.306332252674046</v>
+        <v>-3.034591350676877</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.95027266845365</v>
+        <v>-2.489428447752402</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-7.327403560945164</v>
+        <v>-5.932282316200805</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-5.417058397423055</v>
+        <v>-3.56021948988522</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.082437275985662</v>
+        <v>-3.229992089815291</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.936717448960714</v>
+        <v>-0.7924964182493284</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4.417072173852688</v>
+        <v>-2.928167371452595</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-5.267197358880615</v>
+        <v>-4.193023927118553</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.246144231585291</v>
+        <v>-2.737974048034353</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-5.437567525852764</v>
+        <v>-5.193222451695632</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-5.051370523894441</v>
+        <v>-5.613373305009041</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-8.833907256134275</v>
+        <v>-7.047388692126901</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.02698</t>
+          <t>X &gt; 0.02658</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.439145949452943</v>
+        <v>0.492056942438623</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.074763347724648</v>
+        <v>-0.5785886100846724</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.814487381343852</v>
+        <v>-2.054441075920792</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.80782975435433</v>
+        <v>-3.005297013413511</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-9.964228497516395</v>
+        <v>-6.2462892692119</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-11.91397757103669</v>
+        <v>-4.327293617955199</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-5.257138254601102</v>
+        <v>-2.790382355599739</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.724321653382603</v>
+        <v>-1.095288837224317</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.785321539564904</v>
+        <v>-3.318433155909254</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-7.759042230210802</v>
+        <v>-3.62781141169858</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.469413532056478</v>
+        <v>-3.832512569958773</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-5.682221385946995</v>
+        <v>-4.338674958143983</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-7.226071502509882</v>
+        <v>-5.299366351997939</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-10.34713668708752</v>
+        <v>-6.154711782852488</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02926</t>
+          <t>X &gt; 0.02884</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9309383202099752</v>
+        <v>2.263609516910904</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.5824880668257677</v>
+        <v>0.6524234238470754</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-7.624880639770822</v>
+        <v>-0.4722749682072376</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-5.932127507163322</v>
+        <v>-2.531830846516677</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-17.40804872223549</v>
+        <v>-8.909536458006535</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-24.92310678451983</v>
+        <v>-9.342089435670722</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-10.94534050179211</v>
+        <v>-4.317310743841993</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-12.97502390057361</v>
+        <v>-4.784379387628732</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-9.911023786755912</v>
+        <v>-6.305215558750049</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-10.76114897178384</v>
+        <v>-6.425207347780642</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-5.170054491442293</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.595530353685511</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-8.226773749700889</v>
+        <v>-7.745608214298187</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-11.1020524174246</v>
+        <v>-6.789945556772388</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.03153</t>
+          <t>X &gt; 0.0311</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>0.4036993540810343</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.31929764745994</v>
+        <v>0.7155901840941326</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>0.3208187993390936</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-13.29819893573475</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-22.76519157937835</v>
+        <v>-9.702630225552859</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-27.82489249880555</v>
+        <v>-11.32833311899469</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-15.40962621607783</v>
+        <v>-5.643812709030101</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-15.87680961485933</v>
+        <v>-4.187804429739913</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-10.58066664389877</v>
+        <v>-4.248786586262689</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-11.43079182892669</v>
+        <v>-3.175628459515622</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-2.418791156237354</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-8.029733424470272</v>
+        <v>-4.307489926958951</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-8.449988035415174</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-13.55740956028175</v>
+        <v>-7.386520514661221</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.0338</t>
+          <t>X &gt; 0.03336</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-6.27892497665249</v>
+        <v>-0.5206735521696118</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-13.19553281368387</v>
+        <v>-2.105921127400833</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-15.23919272455463</v>
+        <v>-6.737600745717245</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-24.47326611353984</v>
+        <v>-12.0377950607177</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-30.69756330625896</v>
+        <v>-12.93089722155879</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-15.56490571918341</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-18.20600216144318</v>
+        <v>-6.339819081754563</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-9.571349873712435</v>
+        <v>-2.829372666848762</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-10.42147505874036</v>
+        <v>-0.1078628917500524</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-4.104489252623161</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-2.659138278607308</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-4.2697653223969</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-12.93629154785938</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-20 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-20 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,1561 +3904,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.03209</t>
+          <t>X &lt; -0.0322</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-3.083325669088573</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.931098889695974</v>
+        <v>-1.080053930827091</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.021858490663959</v>
+        <v>3.344451792851594</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.499937710227989</v>
+        <v>3.474676936439955</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.787603451677555</v>
+        <v>7.755664491778006</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.91113234591495</v>
+        <v>10.46267707562995</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.000311672120937</v>
+        <v>9.173147439255345</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10.05486740377422</v>
+        <v>9.910898072577048</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>7.819954474113658</v>
+        <v>12.25955447027114</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>9.143742332563988</v>
+        <v>12.61445495104971</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.765075964768151</v>
+        <v>12.40975379278952</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>6.799459122113582</v>
+        <v>13.64895122225328</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.205291467690422</v>
+        <v>12.02398109183143</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.802838886923226</v>
+        <v>11.04489746494954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02982</t>
+          <t>X &lt; -0.02993</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.7323681314029216</v>
+        <v>0.6722371226188031</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.73369774424512</v>
+        <v>0.8628528313567756</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.951732263454993</v>
+        <v>0.4680814466017367</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.14650152509474</v>
+        <v>0.5983065901900986</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.995177084216124</v>
+        <v>5.465422442499815</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.679715796125329</v>
+        <v>8.465499174837596</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.59498207885305</v>
+        <v>7.479887914670527</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.353605131684454</v>
+        <v>6.111918369982881</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.292605245502152</v>
+        <v>9.654539817063721</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.442480060474225</v>
+        <v>7.903720119832954</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.624823510350197</v>
+        <v>8.599919862473669</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.659206667695628</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3.013145605137822</v>
+        <v>7.313246260614676</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.101576614833462</v>
+        <v>7.538981910841208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02755</t>
+          <t>X &lt; -0.02767</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-3.656229017884399</v>
+        <v>-2.149790202719778</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6166398401509809</v>
+        <v>-0.4497180176379203</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.476863546275688</v>
+        <v>-0.8444894023929592</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.42107016725528</v>
+        <v>-0.05201260317545575</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.719858254508694</v>
+        <v>3.383207777503685</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.203346703852262</v>
+        <v>2.356078495880496</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.04417771109444146</v>
+        <v>1.609116480985186</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.139801680821741</v>
+        <v>2.466551148456723</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.241592492313849</v>
+        <v>5.716827270079648</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.391467307285922</v>
+        <v>4.866908473749788</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.023923285293932</v>
+        <v>4.662207315489596</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.058306442639363</v>
+        <v>6.683340434732337</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.8503202613287968</v>
+        <v>3.614182958902369</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.887773163970749</v>
+        <v>4.502170264758043</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02528</t>
+          <t>X &lt; -0.02541</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.869585109200798</v>
+        <v>-2.980916030534353</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.9408596264587956</v>
+        <v>-0.09210212359818115</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.380853305183308</v>
+        <v>-0.4868735083532201</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.015693593754115</v>
+        <v>0.1433516352351489</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6.559841186021387</v>
+        <v>2.60506208213944</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.270127160434299</v>
+        <v>3.402436111774527</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.18539344316202</v>
+        <v>2.817725752508359</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.387934815022724</v>
+        <v>3.850657108721627</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.409503736179865</v>
+        <v>5.789674952198851</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.476809743812495</v>
+        <v>5.939756155868992</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.437194034173814</v>
+        <v>4.235054997608799</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4.306439576840347</v>
+        <v>5.769433149964122</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.968753773234887</v>
+        <v>2.849282296650713</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.053337490832277</v>
+        <v>2.075017946877246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.023</t>
+          <t>X &lt; -0.02315</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.523741350513006</v>
+        <v>-2.060747963307463</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.347436175598475</v>
+        <v>-1.991261787463721</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.7120018518920403</v>
+        <v>-2.38603317221876</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.721281583745771</v>
+        <v>-1.835639961403508</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.940436126249359</v>
+        <v>0.9874150233159185</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.449999276086224</v>
+        <v>1.284789052951005</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.365265558813945</v>
+        <v>2.040414828138616</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.170809432759725</v>
+        <v>2.413682318805655</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.624961061728939</v>
+        <v>4.873708565644229</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.289987391852527</v>
+        <v>5.284293970995044</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.32765830995919</v>
+        <v>4.239256678281066</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.119617224880379</v>
+        <v>5.113970965090175</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.699362613935477</v>
+        <v>3.433315910096091</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>2.818715425868845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.02073</t>
+          <t>X &lt; -0.02089</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>166</v>
+        <v>305</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-1.005506194468772</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7142651752595057</v>
+        <v>-0.9773480252375322</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.536263938542433</v>
+        <v>0.2672248523025118</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.871336348258367</v>
+        <v>-0.9140254139451827</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.935324771740412</v>
+        <v>1.826373557549289</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.027947432347638</v>
+        <v>3.107354144561427</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.943213715075359</v>
+        <v>3.678381490213283</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.885668870510735</v>
+        <v>3.211312846426544</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>6.222259345774205</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.179363076408933</v>
+        <v>5.579100418164074</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.974609752091354</v>
+        <v>5.04653040744487</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>7.008992909436785</v>
+        <v>5.408777412259205</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>7.19114793704609</v>
+        <v>4.005020001568745</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.645688546430819</v>
+        <v>3.247149094418234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01846</t>
+          <t>X &lt; -0.01863</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>216</v>
+        <v>413</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.6415864683581276</v>
+        <v>-0.4228046503890752</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>0.3873167626003706</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.222341582451399</v>
+        <v>1.203199130871965</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.27852064098483</v>
+        <v>1.575555025065647</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.81417349998673</v>
+        <v>2.974311476812574</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.574578400665352</v>
+        <v>4.482339259474287</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.637992831541226</v>
+        <v>4.155498149602799</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.559698321648611</v>
+        <v>5.141214009448014</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.961661398429271</v>
+        <v>6.290885605951878</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.963388065253199</v>
+        <v>6.651620562648652</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>5.478396401967153</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.79301789828105</v>
+        <v>5.754905304927803</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.90980032437318</v>
+        <v>4.366231449193087</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>7.474336471464284</v>
+        <v>3.381313346392986</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01619</t>
+          <t>X &lt; -0.01637</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>282</v>
+        <v>530</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.429608532975934</v>
+        <v>0.1605934034279102</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.923356861152008</v>
+        <v>1.379595989609363</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>5.783807303491585</v>
+        <v>2.871617057684517</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.914060436099085</v>
+        <v>3.190521446555898</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.375639221026915</v>
+        <v>4.161665855724351</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.382301016898609</v>
+        <v>5.779794602340573</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3.460687867002214</v>
+        <v>5.129046507225347</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.766554113610788</v>
+        <v>5.982732580419736</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.060164156506495</v>
+        <v>7.242505140878094</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.692308475024667</v>
+        <v>7.335982570963331</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.487555150707088</v>
+        <v>6.376564431571062</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.16732837897451</v>
+        <v>6.599621829209404</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.037853909873576</v>
+        <v>5.236074749480899</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.351405029383905</v>
+        <v>3.952376437443284</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01392</t>
+          <t>X &lt; -0.01411</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>369</v>
+        <v>677</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.00292341506092</v>
+        <v>0.6948594495247349</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.6375354923000174</v>
+        <v>1.447041155574638</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.036704726082831</v>
+        <v>2.381664157821085</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.792974118852946</v>
+        <v>3.398152226077087</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.628536643618162</v>
+        <v>3.598415110204435</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.73898671141513</v>
+        <v>5.372894014285613</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.028236733980251</v>
+        <v>5.140473167574832</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.374061465280043</v>
+        <v>5.26424647356653</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.939077839260356</v>
+        <v>7.271211141268267</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.256974334449218</v>
+        <v>8.046107706829105</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.323223720158737</v>
+        <v>6.659722649012053</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.002593327368672</v>
+        <v>6.841811288811982</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.395346846505078</v>
+        <v>5.978528973164742</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.832060048700058</v>
+        <v>4.727159748945198</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01164</t>
+          <t>X &lt; -0.01185</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>460</v>
+        <v>835</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3326486363117596</v>
+        <v>1.171778580244087</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1919684549133649</v>
+        <v>1.117478714725173</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.760988925446568</v>
+        <v>2.638874994640794</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.282546405880161</v>
+        <v>3.128381575354901</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.657168669068859</v>
+        <v>3.54817585459454</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5.60678451982799</v>
+        <v>4.80363371656496</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.348137759077453</v>
+        <v>4.359641920173033</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.402693490730741</v>
+        <v>4.730896629679705</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.428650126287572</v>
+        <v>6.107040221659929</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.66548146299877</v>
+        <v>6.574486694791148</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.330293356072502</v>
+        <v>6.01050409940521</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.277719991678794</v>
+        <v>5.80536129367669</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.857465380733892</v>
+        <v>4.906168524195621</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.107186713010179</v>
+        <v>4.173820342086827</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009372</t>
+          <t>X &lt; -0.009589</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>559</v>
+        <v>1023</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.07841148657848862</v>
+        <v>0.7937662764060178</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.9744215932815621</v>
+        <v>0.06234557923661299</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.208527231427752</v>
+        <v>1.622608407580302</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.664361759384079</v>
+        <v>1.752833551168663</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.979250025528366</v>
+        <v>1.801054262002602</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.350037222635805</v>
+        <v>3.075945398187052</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.118612986579983</v>
+        <v>2.991235038920884</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.619229230016728</v>
+        <v>3.208428369718696</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.273792850095603</v>
+        <v>4.515970162365029</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.85479467759005</v>
+        <v>5.327830447169092</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.186713982968342</v>
+        <v>4.634370735634214</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.505533634052604</v>
+        <v>4.277742045369791</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.264169899673</v>
+        <v>3.271080928126764</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.513891231949287</v>
+        <v>3.008058025078618</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.007099</t>
+          <t>X &lt; -0.007328</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>654</v>
+        <v>1222</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4117604565484356</v>
+        <v>1.037905573393637</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.199813156415821</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.310516913746</v>
+        <v>1.40510685171224</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4.49887402188866</v>
+        <v>1.862664237526467</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.584306017825668</v>
+        <v>1.897206108326024</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.493368750648365</v>
+        <v>2.603745440743445</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.032488244385256</v>
+        <v>2.273535899807882</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.635641237041064</v>
+        <v>2.297465619359933</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.339167344742556</v>
+        <v>3.463979371184116</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.406473352375187</v>
+        <v>4.168888725427088</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.119151220718152</v>
+        <v>3.636855324941045</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.847723980510061</v>
+        <v>3.998565719522219</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.968753773234887</v>
+        <v>2.923750381757095</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.91266470795766</v>
+        <v>2.412988486975443</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004827</t>
+          <t>X &lt; -0.005067</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>765</v>
+        <v>1426</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.970613967371726</v>
+        <v>1.305900238750354</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1180838285990689</v>
+        <v>-0.1650333998955134</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.970707595523294</v>
+        <v>1.403729577200785</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>1.463828493580166</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.784761735280853</v>
+        <v>1.837179894201157</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.559327856003051</v>
+        <v>2.204680151045224</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.298123550495468</v>
+        <v>2.119969791779056</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.007410739949272</v>
+        <v>2.213910965664127</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.207848762263701</v>
+        <v>2.924317308440088</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.749880439980871</v>
+        <v>3.266544374662814</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.590878749650216</v>
+        <v>2.991716989193655</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.096221368757945</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.074288341802379</v>
+        <v>2.185186924981707</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.193290719830301</v>
+        <v>1.92003898474541</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.002555</t>
+          <t>X &lt; -0.002807</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>917</v>
+        <v>1682</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.159778691785661</v>
+        <v>1.264624992057797</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3427436670891737</v>
+        <v>0.4263283163542582</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.661515216281522</v>
+        <v>1.755694862633703</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.882280889783239</v>
+        <v>1.172483620966418</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.798603404263964</v>
+        <v>1.347630453126371</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.768891579711351</v>
+        <v>1.288286290133634</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.138901591991974</v>
+        <v>1.500841091390647</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9988719554787338</v>
+        <v>1.21213154391782</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.265025831564706</v>
+        <v>1.864585772650692</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.178259425162722</v>
+        <v>2.32263368262285</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.845916133560515</v>
+        <v>2.236838588571942</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.77124803681653</v>
+        <v>2.211763708822623</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.678147188139896</v>
+        <v>1.494347694986033</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.25502228268445</v>
+        <v>1.720083345212565</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002829</t>
+          <t>X &lt; -0.000546</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1082</v>
+        <v>1962</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.480683676093165</v>
+        <v>1.188808740107852</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9781673644228093</v>
+        <v>0.5969906388890749</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.137827308473177</v>
+        <v>0.9667452480178298</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.746823509472542</v>
+        <v>0.8930967932371843</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.931137969076893</v>
+        <v>1.272238432802034</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.027101163724168</v>
+        <v>0.7031496693688268</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9423674464518896</v>
+        <v>1.128123306025188</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.122134140091823</v>
+        <v>0.7629914614229492</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6914484868115522</v>
+        <v>1.211693300822702</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.02616618533261317</v>
+        <v>1.279205697153394</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7456272787599474</v>
+        <v>1.125472938485458</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6875889943308877</v>
+        <v>1.108882691248525</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8218630340329298</v>
+        <v>0.6887318379351157</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.441270133407187</v>
+        <v>1.016404287346163</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001989</t>
+          <t>X &lt; 0.001715</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1215</v>
+        <v>2219</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.086808593370264</v>
+        <v>1.101778877081692</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.285934568883384</v>
+        <v>0.977749160764148</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.384893022780624</v>
+        <v>1.574415360506627</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.243541217116515</v>
+        <v>1.794771193594755</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.128988314801546</v>
+        <v>1.8423311222476</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6980351907888078</v>
+        <v>0.9680061883856155</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.271737687508299</v>
+        <v>1.694472034617426</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.380685975969598</v>
+        <v>1.542860804079893</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.6612498757955336</v>
+        <v>1.842401405556224</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3049518512614284</v>
+        <v>1.848724159474223</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.334766428178419</v>
+        <v>1.64402300121403</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.122236005276932</v>
+        <v>1.63333580881946</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9488949745789483</v>
+        <v>1.258250300255945</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.610138940600095</v>
+        <v>1.70931267423191</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.004261</t>
+          <t>X &lt; 0.003975</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1351</v>
+        <v>2476</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1692835732811488</v>
+        <v>0.6882402068495779</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4068223863523954</v>
+        <v>0.8130250463654818</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6036696560871633</v>
+        <v>1.387167670492161</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.65699971177159</v>
+        <v>1.598135648153999</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.600827017409479</v>
+        <v>1.463560265425677</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4189790142967382</v>
+        <v>0.8323917032157908</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.7780322792729777</v>
+        <v>1.433995433574168</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7960253222243168</v>
+        <v>1.128412457934381</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.07918625899869625</v>
+        <v>1.332485937659271</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1891189939896094</v>
+        <v>1.532647916773676</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6423971117446143</v>
+        <v>1.368334480645956</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2326647990678481</v>
+        <v>1.079610855941503</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1084871681377493</v>
+        <v>0.6998477247605734</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4322277454177339</v>
+        <v>0.9255833749871059</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.006534</t>
+          <t>X &lt; 0.006236</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1493</v>
+        <v>2720</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9560051651297599</v>
+        <v>0.1236327589007189</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5622311845111341</v>
+        <v>0.2732683826380651</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.7565651317494257</v>
+        <v>0.6855402847502248</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.579570353799241</v>
+        <v>1.292654643305568</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.107994058513171</v>
+        <v>1.377989448243632</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2690723598651985</v>
+        <v>0.7949526194781242</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5185632415233954</v>
+        <v>1.260499046712326</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.8240981730049839</v>
+        <v>1.086900689059114</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1981629602320396</v>
+        <v>1.193344676969495</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1512506266097375</v>
+        <v>1.428742940009961</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.8166445579815758</v>
+        <v>0.988084744211811</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3824868853404055</v>
+        <v>0.8598078744314321</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4690149308081502</v>
+        <v>0.7913991654489436</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.5177985537743268</v>
+        <v>0.9647238292301807</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.008806</t>
+          <t>X &lt; 0.008497</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1625</v>
+        <v>2957</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6825113711614819</v>
+        <v>0.1684258526921099</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.3296896495646635</v>
+        <v>0.3459674005327713</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4790089393411137</v>
+        <v>0.5586884221226498</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.492864819417406</v>
+        <v>1.026409347013747</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9544436043452365</v>
+        <v>0.8593651533510567</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3310752289853909</v>
+        <v>0.4142484641201278</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5532782827382832</v>
+        <v>0.700783464286971</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.7342819962322906</v>
+        <v>0.5374610236726909</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.02991591951558803</v>
+        <v>0.7991280244473344</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.08102450958347163</v>
+        <v>1.217702795517759</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6976272060497735</v>
+        <v>0.9985685111223077</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1788450284228702</v>
+        <v>0.8495277765271467</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4697975910125223</v>
+        <v>0.6853201600719458</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.3854475825753951</v>
+        <v>0.9642638041650429</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.01108</t>
+          <t>X &lt; 0.01076</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1737</v>
+        <v>3172</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.000901006777134</v>
+        <v>0.2881210997362587</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5458844934497833</v>
+        <v>0.5649148682205691</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4815109497593397</v>
+        <v>0.6736047798783744</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.256090058852756</v>
+        <v>0.9926279096215467</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8898846876382223</v>
+        <v>0.8948669908870883</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.4410579686374589</v>
+        <v>0.4999817379545206</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.9623275051004825</v>
+        <v>0.9501990061269936</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.9869013867827121</v>
+        <v>0.9865916587530918</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.2681380878846866</v>
+        <v>1.19508886469491</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.006943968908622367</v>
+        <v>1.433458926649841</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7658760247726448</v>
+        <v>1.120881769262347</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3977289923538478</v>
+        <v>1.015809961558325</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.7005133619216579</v>
+        <v>0.9288599833825089</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.6378367593169116</v>
+        <v>1.267325639184932</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.01335</t>
+          <t>X &lt; 0.01302</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1834</v>
+        <v>3359</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.8893056394051939</v>
+        <v>0.3117161738625498</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3801614709665131</v>
+        <v>0.6910232477624803</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.666275419542437</v>
+        <v>0.652758101866624</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9321669463440116</v>
+        <v>0.8126920986932475</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3393683522615163</v>
+        <v>0.5120733715036749</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1474138788841941</v>
+        <v>0.2449791896117262</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5821350150740514</v>
+        <v>0.5464839224430094</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.6349720166827879</v>
+        <v>0.5415932157052836</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.1036980786949115</v>
+        <v>0.4377130021394038</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4636271852914717</v>
+        <v>0.645078784474407</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1486129544432444</v>
+        <v>0.3977557709579926</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1285298808518576</v>
+        <v>0.3597336557659716</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.3929469587459735</v>
+        <v>0.2540442014126185</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.4556765902089879</v>
+        <v>0.4371793044241414</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01562</t>
+          <t>X &lt; 0.01528</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1909</v>
+        <v>3512</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.08278001299994</v>
+        <v>0.3750089481527752</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4477496552222959</v>
+        <v>0.5541041850122213</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6336319459359174</v>
+        <v>0.6708417516638292</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.011772701823098</v>
+        <v>0.6589810754170102</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4211048827801775</v>
+        <v>0.4901146538927819</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.2483273847591647</v>
+        <v>0.4464827159234446</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.7672836487567665</v>
+        <v>0.7596126521957771</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.5383129195100693</v>
+        <v>0.706256881319689</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1214829704293905</v>
+        <v>0.8033229476495194</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2390074228565737</v>
+        <v>0.9363431865857166</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3934972329409732</v>
+        <v>0.6625087671678358</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.375551766529199</v>
+        <v>0.6846295073915556</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6132131612938778</v>
+        <v>0.6222683484582845</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.7881715218105967</v>
+        <v>0.8358379924353372</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01789</t>
+          <t>X &lt; 0.01754</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1982</v>
+        <v>3648</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.9584609674168192</v>
+        <v>0.3090183239514275</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.55694952753759</v>
+        <v>0.4210269792464558</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.7001826025287485</v>
+        <v>0.5733015463513738</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6882486881059293</v>
+        <v>0.4449932221024397</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1498274730337599</v>
+        <v>0.3444601669547609</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1956337791439822</v>
+        <v>0.5050352909811053</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.5916685616519928</v>
+        <v>0.7760020862976944</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.5049823966556062</v>
+        <v>0.7893544267292825</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2336044319172004</v>
+        <v>0.7710601150786758</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.2268747782354552</v>
+        <v>0.840084742944569</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5260331877695421</v>
+        <v>0.6509684459791103</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3084002160827239</v>
+        <v>0.5639536979093265</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.723522518579486</v>
+        <v>0.5430340094487391</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.8003819922625794</v>
+        <v>0.6199740872281225</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.02017</t>
+          <t>X &lt; 0.0198</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2035</v>
+        <v>3753</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.122233618936711</v>
+        <v>0.174421197293583</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7488139909890279</v>
+        <v>0.1177252336395327</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.702722384013839</v>
+        <v>0.3484081069496483</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.75041168930899</v>
+        <v>0.3071836841322977</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.4569684262211524</v>
+        <v>0.3150567658183476</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2913539997938983</v>
+        <v>0.3346349950502656</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3806771539214751</v>
+        <v>0.4507044759126231</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2839922917718312</v>
+        <v>0.3441394178463923</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3388895206783431</v>
+        <v>0.457583414146697</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3544540773312121</v>
+        <v>0.5008421287196683</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3244450283953881</v>
+        <v>0.3910720370124139</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1133691773952137</v>
+        <v>0.3340137092184534</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.6048814565859502</v>
+        <v>0.3817809647380841</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.538764535892355</v>
+        <v>0.4628410217506769</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.02244</t>
+          <t>X &lt; 0.02206</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2072</v>
+        <v>3836</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.122586949358606</v>
+        <v>0.1561325535134515</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.640141865801759</v>
+        <v>0.2218271903311262</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7943945954974794</v>
+        <v>0.3870542275448798</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.6351848123746962</v>
+        <v>0.3235388427234369</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.4817491603439166</v>
+        <v>0.4236576608130491</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2762492578489741</v>
+        <v>0.2411457891938866</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2661238527358236</v>
+        <v>0.2747905456387372</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1145845331613344</v>
+        <v>0.08230729091839351</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4501390230143514</v>
+        <v>0.2439837259556867</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4323760691801724</v>
+        <v>0.2939228225356629</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2307587453643549</v>
+        <v>0.182046401620255</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.07227787185153289</v>
+        <v>0.2311319514232153</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.4992573646261675</v>
+        <v>0.3208746865386516</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5352545323823463</v>
+        <v>0.4311180511525308</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.02471</t>
+          <t>X &lt; 0.02432</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2120</v>
+        <v>3917</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.106508371926012</v>
+        <v>-0.0381679389313021</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.5772602868901302</v>
+        <v>0.1456173979085662</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.9250923048696009</v>
+        <v>0.1719859621152153</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4751514204001737</v>
+        <v>0.1633414493426031</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.5011704687334699</v>
+        <v>0.3776041096483667</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.3540990978331067</v>
+        <v>0.2559392964879024</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.3894052609197516</v>
+        <v>0.2616605129568867</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2307874512869645</v>
+        <v>0.08899511534921345</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.322487028980234</v>
+        <v>0.271571943529807</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.277230498645288</v>
+        <v>0.3539362119771212</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.413397892399999</v>
+        <v>0.2401570384251244</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.3535303428651275</v>
+        <v>0.391020289540549</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.7143212526564895</v>
+        <v>0.4192159362627592</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.755258903330116</v>
+        <v>0.5063429404948039</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.02698</t>
+          <t>X &lt; 0.02658</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2155</v>
+        <v>3973</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.9670738428741785</v>
+        <v>-0.02231091262165563</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.7038087864828881</v>
+        <v>0.0860660068911514</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.098677493079478</v>
+        <v>0.08139958401626046</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.5123715673392155</v>
+        <v>0.1500049116599556</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.4829739524521486</v>
+        <v>0.3034548495929883</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.5282821043690618</v>
+        <v>0.2379045870320127</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4227697344283641</v>
+        <v>0.1920976118048472</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.351841252345757</v>
+        <v>0.09066716149870757</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3324713991805766</v>
+        <v>0.2446774660248963</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2553828614454048</v>
+        <v>0.2636183635632321</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4207168508619503</v>
+        <v>0.2491395046510476</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2696572636547643</v>
+        <v>0.272577804052176</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.7104943393529197</v>
+        <v>0.3195892921212646</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.6620137078654125</v>
+        <v>0.3583051353997675</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02926</t>
+          <t>X &lt; 0.02884</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2180</v>
+        <v>4021</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.8702101537719358</v>
+        <v>-0.07635480098551994</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.6283422167972859</v>
+        <v>0.03633824337429559</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.9774652692310255</v>
+        <v>0.002213793234083994</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.5251574882621171</v>
+        <v>0.09634096790694002</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5814297773070507</v>
+        <v>0.3159801962833697</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.7669675861895513</v>
+        <v>0.3540370052965045</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5244397179881162</v>
+        <v>0.2084903999760925</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4948283669481413</v>
+        <v>0.2020353058907389</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.2739362523837769</v>
+        <v>0.3038329253732215</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.2533006674758624</v>
+        <v>0.3124269633224088</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.4585362923495424</v>
+        <v>0.2459893912469653</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2179423644520782</v>
+        <v>0.2944145071602478</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.6488853516287776</v>
+        <v>0.3358561405094918</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.5579246467955841</v>
+        <v>0.3022002398392019</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.03153</t>
+          <t>X &lt; 0.0311</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2188</v>
+        <v>4054</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.8305681607566768</v>
+        <v>-0.009807105036443886</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.5498615229645694</v>
+        <v>0.03972276572793731</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8991513781482183</v>
+        <v>-0.02192885890673324</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.6896249996735051</v>
+        <v>0.1216980919280601</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.6525711501437215</v>
+        <v>0.261350538944761</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.7473503518230729</v>
+        <v>0.3261190265948173</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.5966303011275969</v>
+        <v>0.2056843833874638</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.5198129319229707</v>
+        <v>0.1462236111846806</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2920169374408417</v>
+        <v>0.1974108477396257</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2745622137929686</v>
+        <v>0.1743544801666701</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.43392647102187</v>
+        <v>0.1314069818335994</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2399991260842</v>
+        <v>0.1796895602205311</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.6221584111031362</v>
+        <v>0.2420073274768555</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5781349683158012</v>
+        <v>0.2597737436212029</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.0338</t>
+          <t>X &lt; 0.03336</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2198</v>
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.838109522024034</v>
+        <v>-0.02189963709172815</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.4752478678384833</v>
+        <v>0.06844608981347022</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.9154886252517684</v>
+        <v>0.02965035945583594</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.6666701334900296</v>
+        <v>0.1487385108472878</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.5819694265848412</v>
+        <v>0.2605849819680017</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.67763652006483</v>
+        <v>0.3019951514609645</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.5271844755012651</v>
+        <v>0.1572258750273576</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.4939958631701415</v>
+        <v>0.1692845597020209</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3598874231195524</v>
+        <v>0.146380026972075</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3463762445111129</v>
+        <v>0.09473408622700674</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.3579613402622215</v>
+        <v>0.07550140428037366</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1650717703349187</v>
+        <v>0.1237020410338019</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.5435479874523637</v>
+        <v>0.1590982475709666</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.5008251985899577</v>
+        <v>0.2024111722086133</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_20.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_20.xlsx
@@ -568,1509 +568,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.03106</t>
+          <t>X ≈ -0.03107</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.028671230991314</v>
+        <v>8.999648757688504</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.589731124105562</v>
+        <v>3.588575783539916</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-12.14644883956036</v>
+        <v>-12.14668953712949</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-12.01946104607091</v>
+        <v>-12.02003349976631</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-4.884446628347817</v>
+        <v>-4.836038303016657</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.7503204678928839</v>
+        <v>-0.7264133115181295</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.8349321627706416</v>
+        <v>-0.7870078332378441</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.982453649469669</v>
+        <v>-8.933315248944915</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.362714118529397</v>
+        <v>-1.289552835121121</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.896799495949907</v>
+        <v>-9.797578038082747</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.260456215273273</v>
+        <v>-6.160635649944275</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.383349113462884</v>
+        <v>-2.259717584193865</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-10.49432665677489</v>
+        <v>-10.34568145887784</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.424982053120999</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.0288</t>
+          <t>X ≈ -0.02881</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-9.948697198586522</v>
+        <v>-11.44749687801264</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.079780753580103</v>
+        <v>-5.359235556787461</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-4.474662563077992</v>
+        <v>-3.196299798562492</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.852041679925605</v>
+        <v>-0.5097358995412762</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.389876801378762</v>
+        <v>-0.9983110691818666</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-14.56886755373438</v>
+        <v>-13.52144024713624</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-14.65692021403872</v>
+        <v>-13.58521187393718</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.638097979064476</v>
+        <v>-6.372826078677811</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.204050682346995</v>
+        <v>-3.85044739859984</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.556816463701551</v>
+        <v>-2.1127656302695</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.260382334985493</v>
+        <v>-4.879469516641841</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-3.72881387893257</v>
+        <v>-2.259701438481876</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.649090522926819</v>
+        <v>-5.218711571928381</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.924982053122754</v>
+        <v>-2.406829447402245</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.02654</t>
+          <t>X ≈ -0.02655</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.523730956974973</v>
+        <v>-4.495080642901733</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.007114499053401</v>
+        <v>1.901225345247759</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.613511870065615</v>
+        <v>-0.4856689922014965</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7435448991986036</v>
+        <v>-0.3562483620860135</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.206374267535324</v>
+        <v>-0.8447698688376235</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.613453320197756</v>
+        <v>5.415344141250486</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.530667962814796</v>
+        <v>5.35626554803796</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>8.103597891228311</v>
+        <v>6.889385510210786</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.00641841448985</v>
+        <v>4.85663491781736</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.236454028454972</v>
+        <v>8.030901961323124</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.916438081382921</v>
+        <v>1.833484008146591</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.951523395376398</v>
+        <v>1.89207537206223</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4919989922233086</v>
+        <v>-0.5019228884555176</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.404573889857446</v>
+        <v>-6.252983293557001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02428</t>
+          <t>X ≈ -0.02429</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.773543535617826</v>
+        <v>2.74447220401035</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-11.95006101618186</v>
+        <v>-11.95134713049592</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.34693393103856</v>
+        <v>-12.34718371330153</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-12.22020297818217</v>
+        <v>-12.22078320368691</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.509546542995906</v>
+        <v>-7.461164309123824</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-9.840913039903306</v>
+        <v>-9.817061552988775</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.04718158296123</v>
+        <v>-1.999269414797133</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.141709236782845</v>
+        <v>-5.092561577968667</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.05250886451314329</v>
+        <v>0.1256693526572334</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.832414396169398</v>
+        <v>1.931661502000168</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.258002861192395</v>
+        <v>4.35784018867114</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.66320893351044</v>
+        <v>1.786842150400815</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.505499412909671</v>
+        <v>6.654153783475216</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.732912683719348</v>
+        <v>6.904911443287212</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02202</t>
+          <t>X ≈ -0.02203</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>67</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.734162068309189</v>
+        <v>2.705094403055334</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.616728361900883</v>
+        <v>2.615565464742929</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.665010072300653</v>
+        <v>9.664933386632001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2.353976000745583</v>
+        <v>2.353498442129975</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4.795245356101908</v>
+        <v>4.843703471312089</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>9.561603623831743</v>
+        <v>9.58556515232199</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9.479498419195906</v>
+        <v>9.527467123700944</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.035123763643647</v>
+        <v>6.084317591832701</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.485082571017074</v>
+        <v>4.558256815951239</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.619218642410729</v>
+        <v>6.718477321096074</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.907857939815642</v>
+        <v>8.00770169225197</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.452527045003777</v>
+        <v>6.576165687883453</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.034248430129985</v>
+        <v>6.18290162706068</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.769047797623514</v>
+        <v>4.941046557190177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01976</t>
+          <t>X ≈ -0.01977</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>108</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.218833994165877</v>
+        <v>1.189758126624653</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.228125875698858</v>
+        <v>4.226980196593829</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.835090851776208</v>
+        <v>3.834971440356256</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.583615774728706</v>
+        <v>8.583188381134974</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.20095724682843</v>
+        <v>6.249422694764682</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8.347124822516818</v>
+        <v>8.37108168338618</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5.492222082029464</v>
+        <v>5.540169369303129</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>10.57411569213206</v>
+        <v>10.6233295907872</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>10.51599448064385</v>
+        <v>10.58918925147116</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>9.66980192479042</v>
+        <v>9.769066981154779</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.692395628969201</v>
+        <v>6.792234401125363</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.728613099005841</v>
+        <v>6.852249948650304</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.384816901428167</v>
+        <v>5.533468116463744</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.760203132062856</v>
+        <v>3.932201891629092</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.0175</t>
+          <t>X ≈ -0.01751</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>117</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.212180393475357</v>
+        <v>2.183123374266863</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.866228162919775</v>
+        <v>4.865093824828861</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.734062138103013</v>
+        <v>8.733991710270189</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.86632907828492</v>
+        <v>8.865912414760302</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>8.331480525407407</v>
+        <v>8.379959792224696</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>10.33590808120191</v>
+        <v>10.35988155374507</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>8.548340656684744</v>
+        <v>8.59630376025838</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>8.937573774492215</v>
+        <v>8.986780661824703</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>10.5862283880585</v>
+        <v>10.6594223017339</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>9.740286007869699</v>
+        <v>9.839548220523653</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>9.538696182968209</v>
+        <v>9.638538837847406</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>9.575811765135164</v>
+        <v>9.699450371837749</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.304146977847907</v>
+        <v>8.452798536678422</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.968180340039254</v>
+        <v>6.1401790996063</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01524</t>
+          <t>X ≈ -0.01525</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>147</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.6112876295578</v>
+        <v>2.582247587327501</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.683936759879856</v>
+        <v>1.682775750916086</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6118637500874797</v>
+        <v>0.6117253912052618</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.133575803513246</v>
+        <v>4.133128229674</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.562077977893452</v>
+        <v>1.610502337910532</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.895042352060884</v>
+        <v>3.918976185816589</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.169908612326161</v>
+        <v>5.217850805414855</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.667759137506074</v>
+        <v>2.71693270277823</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7.362757803611174</v>
+        <v>7.435936058971954</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.59313954640197</v>
+        <v>10.69240114427828</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>7.673284911513733</v>
+        <v>7.773119554941601</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>7.710072405882443</v>
+        <v>7.833704588367461</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>8.652722295417107</v>
+        <v>8.801371871664266</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>7.520596178169768</v>
+        <v>7.69259493773643</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01298</t>
+          <t>X ≈ -0.01299</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.202234586198536</v>
+        <v>2.961723238441941</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2943397292604573</v>
+        <v>-0.5437090102515612</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.727055718503046</v>
+        <v>3.564170726753645</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.964606048004782</v>
+        <v>1.764668403668452</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.322063147554111</v>
+        <v>3.207610967103214</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.356379756387916</v>
+        <v>2.192927242559414</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.009849221058843</v>
+        <v>0.8458764331342863</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.439425667140902</v>
+        <v>2.313331809987119</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.115141348665432</v>
+        <v>0.9885060998884114</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2667977481043309</v>
+        <v>0.1661744275538979</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.224719263600768</v>
+        <v>3.18583238726427</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.362797769331962</v>
+        <v>1.310937744386273</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3108892873874041</v>
+        <v>0.2717526647602853</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.802866048143066</v>
+        <v>1.811532835476171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.01072</t>
+          <t>X ≈ -0.01073</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8827245385795166</v>
+        <v>-0.6759788892805005</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.607182037751301</v>
+        <v>-4.339267371882947</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.883389339839674</v>
+        <v>-2.6476298682174</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.345248178641235</v>
+        <v>-4.084784618985616</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.944210152335025</v>
+        <v>-5.618153192926734</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.588814524727191</v>
+        <v>-4.303808012287995</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.081922490612627</v>
+        <v>-2.797836811020247</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.548986045009251</v>
+        <v>-3.26357803796877</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.548956816620411</v>
+        <v>-2.256168519082912</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.2108715963756964</v>
+        <v>0.05800640185304928</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.47765989350313</v>
+        <v>-1.191446748581512</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.506439777629019</v>
+        <v>-2.179666574742988</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.99023576055292</v>
+        <v>-3.621667546065119</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.169662904186588</v>
+        <v>-1.802721513451381</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.008459</t>
+          <t>X ≈ -0.008468</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.28171118028434</v>
+        <v>2.528156583488688</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.823120557218402</v>
+        <v>-1.561456888027081</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2838889773499744</v>
+        <v>0.5593633280128358</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.417141438374458</v>
+        <v>2.199171669308782</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.382446164255228</v>
+        <v>2.719283011610109</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1732324880728271</v>
+        <v>0.473012110554798</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.414703223134637</v>
+        <v>-1.09845597314807</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.382687136321117</v>
+        <v>-2.067634539819984</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.942995138019668</v>
+        <v>-1.601332829098652</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.788652048387398</v>
+        <v>-1.9201170634229</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.49100422295372</v>
+        <v>-1.114872196039236</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.5607693149448</v>
+        <v>2.47639789687036</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.137507604430972</v>
+        <v>1.07301923140755</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.6460875807609483</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.006197</t>
+          <t>X ≈ -0.006209</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.89542007389776</v>
+        <v>2.597476421953971</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3190604806177504</v>
+        <v>0.05353349112871797</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.387470863978258</v>
+        <v>1.115778487035257</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.9246677684499289</v>
+        <v>-0.6987560269270432</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.47023342530607</v>
+        <v>1.244444149573816</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1882668863401094</v>
+        <v>-0.4290914747017425</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.194814706535269</v>
+        <v>0.9707326855121323</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.707674080906266</v>
+        <v>1.479985286023854</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3102070241564903</v>
+        <v>-0.5044833235279214</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.137894202519817</v>
+        <v>-1.814278824046454</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8733843761078006</v>
+        <v>-1.043554020992929</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.308455817719036</v>
+        <v>-1.960264916330637</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.238542791850122</v>
+        <v>-1.867624289637313</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.03282519037765</v>
+        <v>-0.6432271959951095</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.003937</t>
+          <t>X ≈ -0.003949</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>256</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.025765417015201</v>
+        <v>0.9968545666223747</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.70328219342673</v>
+        <v>3.702176145307789</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.696496869599095</v>
+        <v>3.696444692822354</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4515880136695785</v>
+        <v>-0.4520623044317347</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.377709272364868</v>
+        <v>-1.329424006284661</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.807546095519911</v>
+        <v>-3.783730539646605</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.945263753569961</v>
+        <v>-1.897457987506883</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.36018119735224</v>
+        <v>-4.311138910972666</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.033117170012538</v>
+        <v>-3.960096799592513</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.933033176332586</v>
+        <v>-2.833929115836185</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.967451403509656</v>
+        <v>-1.867722869306796</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.713971118498144</v>
+        <v>-2.590425707813793</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.353309936453002</v>
+        <v>-2.204712355327864</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6062679468772458</v>
+        <v>0.7782667064439082</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001677</t>
+          <t>X ≈ -0.001689</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7240294208440829</v>
+        <v>0.5284841771077708</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.612316352166225</v>
+        <v>1.453326132370499</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.759814661368878</v>
+        <v>-3.579138880887605</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7851807194519367</v>
+        <v>-0.5945096601325517</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8123671369581018</v>
+        <v>0.7025494566314805</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.80459550190907</v>
+        <v>-2.952997146017545</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.110228679761988</v>
+        <v>-1.228347650836696</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.931849182585999</v>
+        <v>-2.050070864896391</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.706710571877693</v>
+        <v>-2.803606760927742</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.982332239606421</v>
+        <v>-5.05836528931664</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-5.545002336855887</v>
+        <v>-5.621756478025347</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.512524694168803</v>
+        <v>-5.207424319807217</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.149237081170057</v>
+        <v>-3.812580305034594</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.210696338836961</v>
+        <v>-2.847965372409135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005845</t>
+          <t>X ≈ 0.000571</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.4274334116754517</v>
+        <v>0.5801173714775061</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.858053312916624</v>
+        <v>4.019054284442412</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>6.173474388357945</v>
+        <v>5.93948324349352</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8.629864794355768</v>
+        <v>8.386468438110292</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.160817120913784</v>
+        <v>6.359374135388158</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.975400523443803</v>
+        <v>3.163068205947013</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>5.993258371482646</v>
+        <v>6.192954055125277</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>7.471570204848881</v>
+        <v>7.665083471426662</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>6.637898261863334</v>
+        <v>6.858395893155802</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>6.181813255074616</v>
+        <v>6.426901424206221</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>5.592750692002312</v>
+        <v>5.840034308553534</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>5.630440688804221</v>
+        <v>5.514361763305473</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>5.602952816512058</v>
+        <v>5.510321890203699</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>6.999142460495833</v>
+        <v>6.925311280087229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.002845</t>
+          <t>X ≈ 0.002831</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>257</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.863305304438214</v>
+        <v>-3.079423008064779</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.6047494972673846</v>
+        <v>-0.7872917188909483</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2265686633973445</v>
+        <v>-0.410515554096861</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.09588334242535268</v>
+        <v>-0.2817491649562243</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.794401563416933</v>
+        <v>-1.929094497878502</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3341850498113246</v>
+        <v>-0.4906446317007038</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.8059830957080081</v>
+        <v>-0.9415182568045779</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.436858001093078</v>
+        <v>-2.567928163752796</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.066832575784929</v>
+        <v>-3.381987968990025</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.198140544605707</v>
+        <v>-1.48744721286409</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.01331129731043</v>
+        <v>-1.302173860012132</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.699033848692757</v>
+        <v>-3.964300406392141</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.11985232732134</v>
+        <v>-4.360233324431718</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.841324465574118</v>
+        <v>-5.669325706007363</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.005106</t>
+          <t>X ≈ 0.00509</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.562742335974619</v>
+        <v>-5.505392027743369</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.161871132415968</v>
+        <v>-5.071761205247832</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.365832167046818</v>
+        <v>-6.276526060615076</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.736135765317094</v>
+        <v>-1.327243251540935</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.57524979802659</v>
+        <v>0.6021050402014154</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4522056750366303</v>
+        <v>0.4782002557278773</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4358960505020022</v>
+        <v>-0.793885504975357</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.7197913755839167</v>
+        <v>0.3573779676777278</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.1584335341043328</v>
+        <v>-0.08221044837363678</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4310149311251834</v>
+        <v>0.3077435355385205</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.835699489913708</v>
+        <v>-3.126096933131684</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.351960097962412</v>
+        <v>-1.855414355025587</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.727178909841463</v>
+        <v>0.9864682763916051</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.36190319277889</v>
+        <v>0.4271786497637464</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.007366</t>
+          <t>X ≈ 0.00735</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.6783363337281472</v>
+        <v>0.03037175604270459</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.174530733720907</v>
+        <v>0.5590007775074923</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9021722380294221</v>
+        <v>-1.518894683921701</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.037231110010538</v>
+        <v>-2.660357425292126</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.099590080684145</v>
+        <v>-5.250500916571582</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.960393920505325</v>
+        <v>-4.131881228482797</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.734196582071334</v>
+        <v>-5.462792710126621</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.782254283683436</v>
+        <v>-5.50610157883856</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.73353179885595</v>
+        <v>-3.858491933527539</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.207923169025527</v>
+        <v>-1.303875421700653</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.119021242334583</v>
+        <v>1.031546489672245</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.7314584664197668</v>
+        <v>0.6692386605590883</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5325742434336718</v>
+        <v>-0.5704718508888078</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9589841916029798</v>
+        <v>0.1029489098337919</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.009628</t>
+          <t>X ≈ 0.00961</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.921129227283721</v>
+        <v>2.546821040229972</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.55669465513256</v>
+        <v>4.641031541738784</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.238764643708286</v>
+        <v>3.33260865759641</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5148846825860289</v>
+        <v>0.7043204577820319</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.37365111297364</v>
+        <v>2.06039879532571</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.676283239240419</v>
+        <v>2.344890953881915</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.381507004124302</v>
+        <v>4.122069051429378</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>7.176238504070518</v>
+        <v>7.348095460589064</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.650140068477924</v>
+        <v>6.856818952984838</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.404872434938753</v>
+        <v>4.657449514862506</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.804822439469156</v>
+        <v>3.078144013163481</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.304316870894411</v>
+        <v>3.142245780317495</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.279514854790243</v>
+        <v>4.602936985760479</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.435483063156319</v>
+        <v>5.784053743480847</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.01189</t>
+          <t>X ≈ 0.01187</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7070746643524686</v>
+        <v>1.077299352289899</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.818816158889618</v>
+        <v>2.863297344664062</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.3012153287671993</v>
+        <v>0.6681764466785864</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.227535884258145</v>
+        <v>-1.516230733724989</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-5.967667462772859</v>
+        <v>-5.653847295361956</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-4.07630882749671</v>
+        <v>-3.561173825533039</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-6.296575674058381</v>
+        <v>-4.902218784179276</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-7.021000645289071</v>
+        <v>-6.413433463141871</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-12.42957638469954</v>
+        <v>-11.91000701501469</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-12.74473582274063</v>
+        <v>-12.46501396176442</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-11.87991826442322</v>
+        <v>-11.63169091337722</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-10.77602139549042</v>
+        <v>-10.01608322485622</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-11.19617224880383</v>
+        <v>-10.94219217014302</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-13.64423339002115</v>
+        <v>-13.32104612078116</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01415</t>
+          <t>X ≈ 0.01413</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>153</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.739214628646721</v>
+        <v>2.352943538142696</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.459201598063984</v>
+        <v>-2.479069701230387</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.044839831579289</v>
+        <v>1.023925902994634</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.725603566215085</v>
+        <v>-2.089926775859865</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.000563076267170004</v>
+        <v>0.01221250031556309</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.870708479969601</v>
+        <v>5.481400012275039</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.448444706756732</v>
+        <v>6.080712068319194</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.327781291728193</v>
+        <v>4.653455123216403</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.841962533898197</v>
+        <v>9.169205417572279</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.338448966326553</v>
+        <v>7.694784798002019</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.480153036824483</v>
+        <v>6.54316769838357</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.821720731663468</v>
+        <v>7.916982754881808</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.708759420833715</v>
+        <v>8.842452866923644</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>9.588089842302075</v>
+        <v>9.760088601868738</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01641</t>
+          <t>X ≈ 0.01639</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.387566218157197</v>
+        <v>-1.059407204715342</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.997034373892575</v>
+        <v>-2.643908032043583</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.929518582577217</v>
+        <v>-1.585176410623426</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-5.082686624255381</v>
+        <v>-5.083708597553375</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.421051922490193</v>
+        <v>-3.746737815929393</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.01182098914019</v>
+        <v>1.60583042229203</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.200078693684837</v>
+        <v>0.8105876364599922</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.938892402839237</v>
+        <v>2.526256338452235</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.06326622427173589</v>
+        <v>-0.414339598298028</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.648479138248696</v>
+        <v>-1.962961079644167</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3527020564322854</v>
+        <v>0.01974200578195706</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.55409626180063</v>
+        <v>-2.824829024586819</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.503658879819874</v>
+        <v>-1.760307888632674</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.954393817828674</v>
+        <v>-5.158092782607184</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01867</t>
+          <t>X ≈ 0.01865</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>105</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.399547560816366</v>
+        <v>-3.938398952554309</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-10.34187051344436</v>
+        <v>-10.29108923333355</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.352370584376651</v>
+        <v>-7.81221027244068</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.392849979913862</v>
+        <v>-4.848211747313385</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6575867273843841</v>
+        <v>-1.556502550532016</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-5.562059275421426</v>
+        <v>-6.01151922326698</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-10.87275043796782</v>
+        <v>-11.74361281909221</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-15.1493428912784</v>
+        <v>-16.01607222740549</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-10.44842028589638</v>
+        <v>-11.31240848989014</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-11.29833908222627</v>
+        <v>-13.09270654084943</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-8.645897383343531</v>
+        <v>-9.522305728201502</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-7.65913827860728</v>
+        <v>-9.48643564740803</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.222146274777884</v>
+        <v>-8.434583278788033</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-4.996410624551238</v>
+        <v>-7.681554722127522</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.02093</t>
+          <t>X ≈ 0.02091</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.6736871148717327</v>
+        <v>-1.349028693014219</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.944042454715039</v>
+        <v>4.031265164429179</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.139632515743173</v>
+        <v>1.311576101571504</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.065038382223058</v>
+        <v>0.2837833406309258</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.346025937561173</v>
+        <v>4.43281102989468</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.995154249671252</v>
+        <v>-5.728633913872983</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-7.694322440262717</v>
+        <v>-9.269133068999466</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-11.77584891537472</v>
+        <v>-13.20799623584853</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-9.427192517680666</v>
+        <v>-10.92810131635586</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-9.072292036902056</v>
+        <v>-9.431277557744131</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-9.276993195162284</v>
+        <v>-9.632390156642387</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-4.423337934373194</v>
+        <v>-3.781288833658792</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.433850233469741</v>
+        <v>-0.6880746671993663</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.003295306134838</v>
+        <v>0.723760892490418</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.02319</t>
+          <t>X ≈ 0.02317</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>81</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-9.271039487324437</v>
+        <v>-9.923252519761384</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.474818172980918</v>
+        <v>-4.118133155733311</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-10.04242906390876</v>
+        <v>-10.6541331170633</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.443068117851261</v>
+        <v>-8.066579848313573</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.808518164774128</v>
+        <v>-2.375345099803333</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.3398208799719598</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.3612865931706253</v>
+        <v>-0.9554031104880494</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>1.013500206795491</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.579798408988964</v>
+        <v>2.226384265472007</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.199015415128237</v>
+        <v>3.867869295481484</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.994314256868051</v>
+        <v>3.648440081366658</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.966964014161654</v>
+        <v>8.090660635189899</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.077677358379105</v>
+        <v>5.226366906156933</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>4.068845107371075</v>
+        <v>4.240843866937738</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.02545</t>
+          <t>X ≈ 0.02543</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>2.035342720567556</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-4.09210212359816</v>
+        <v>-3.184198000951881</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.272587794067533</v>
+        <v>-5.396117807448476</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7852197933362675</v>
+        <v>0.188311688311714</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-3.937301089003874</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.026135316796896</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.682274247491662</v>
+        <v>-3.725171659410435</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2077999658644885</v>
+        <v>1.263541034751739</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.638896476372558</v>
+        <v>-0.5916133925668774</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.060243844130987</v>
+        <v>-5.0518056097455</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>2.016781215445654</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-8.016281135750162</v>
+        <v>-7.01596113809854</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-5.592937246480552</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-9.996410624551324</v>
+        <v>-8.980256020828818</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.02771</t>
+          <t>X ≈ 0.02769</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-4.564249363867681</v>
+        <v>-5.571336314682902</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-5.113697073308174</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-6.570206841686549</v>
+        <v>-7.54825138815346</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.356648364764887</v>
+        <v>-5.377551020408198</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.355062082139447</v>
+        <v>0.2556488182317409</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.985769445107877</v>
+        <v>8.691699643173131</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.567725752508331</v>
+        <v>0.4677782478251871</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.433990442054927</v>
+        <v>8.165210793564263</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.206341618865494</v>
+        <v>4.046605531366268</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.356422822535656</v>
+        <v>3.222776950551321</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-1.062996150046004</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.682615629984014</v>
+        <v>0.6408289872856585</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.341648719789418</v>
+        <v>-5.232575130290783</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02997</t>
+          <t>X ≈ 0.02995</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>33</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8.125144575526257</v>
+        <v>8.095948781173625</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.4533524218563372</v>
+        <v>0.4521656354116814</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.971721993201726</v>
+        <v>-2.971875383206047</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.219109210992755</v>
+        <v>3.218614718614752</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-6.410089433012068</v>
+        <v>-6.361543513246296</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.08241237307395</v>
+        <v>-3.058454964124337</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1368197020370232</v>
+        <v>-0.08880802304670254</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-6.664494406429846</v>
+        <v>-6.615246844036129</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-12.78608262355868</v>
+        <v>-12.71282551377898</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-16.66630445019162</v>
+        <v>-16.56695712489704</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-13.84070257814878</v>
+        <v>-13.7407945421301</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-13.80632442579346</v>
+        <v>-13.68262780476521</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-11.19617224880379</v>
+        <v>-11.04748270102596</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.909830537971217</v>
+        <v>-4.737831778404555</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.03223</t>
+          <t>X ≈ 0.03221</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.907897876401847</v>
+        <v>5.906711089957192</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.51312649164678</v>
+        <v>10.51297310164246</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.64335163523517</v>
+        <v>5.642857142857167</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.105062082139483</v>
+        <v>0.1536080019052548</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.597563888225501</v>
+        <v>-4.573606479275888</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-9.682274247491669</v>
+        <v>-9.634262568501349</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-10.21032504780118</v>
+        <v>-10.13706793802149</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-16.06024384413101</v>
+        <v>-15.96089651883644</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-11.2649450023912</v>
+        <v>-11.16503696637253</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-11.23056685003588</v>
+        <v>-11.10687022900763</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-16.65071770334932</v>
+        <v>-16.50202815557149</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.42498205312279</v>
+        <v>-11.25298329355613</v>
       </c>
     </row>
   </sheetData>
@@ -2214,1557 +2214,1557 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4073</v>
+        <v>4084</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.03988671053271275</v>
+        <v>0.04053498985551585</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.05722468178737472</v>
+        <v>0.0571017149571631</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1039156239261914</v>
+        <v>-0.1036325149631594</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.08283009388559748</v>
+        <v>-0.08259473794403505</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1668634445631483</v>
+        <v>-0.1676722326415714</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1991321313031378</v>
+        <v>-0.1992174274674525</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1479605220014406</v>
+        <v>-0.1488066897430613</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1848908196921926</v>
+        <v>-0.1856699010117993</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1833510409350367</v>
+        <v>-0.1847568595181528</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.185826380309571</v>
+        <v>-0.1879023896779231</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2050823919888458</v>
+        <v>-0.2071216250463692</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.2305668500358706</v>
+        <v>-0.2331551041911837</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1951457838598429</v>
+        <v>-0.1984785839680328</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1765165485806435</v>
+        <v>-0.1805053307745084</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02993</t>
+          <t>X &gt; -0.02994</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4047</v>
+        <v>4058</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01786184334223861</v>
+        <v>-0.01686692191473327</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.03453005181447821</v>
+        <v>0.03447521772129392</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.02654822496239007</v>
+        <v>-0.02647147933566885</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.006143065282479654</v>
+        <v>-0.006110408765280795</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1365552748625234</v>
+        <v>-0.1377615579669182</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1955910152291693</v>
+        <v>-0.1958396322517544</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.1435470644625241</v>
+        <v>-0.1447176730523623</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1283707718606593</v>
+        <v>-0.1296228879397745</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1757742087093348</v>
+        <v>-0.1776783244354334</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1234381171500232</v>
+        <v>-0.1263322647743976</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1661795702924351</v>
+        <v>-0.1689768826493037</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.216736274585152</v>
+        <v>-0.220170721618473</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1289785729145052</v>
+        <v>-0.1334644699346086</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1363732070639472</v>
+        <v>-0.141598374876942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02767</t>
+          <t>X &gt; -0.02768</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4007</v>
+        <v>4019</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.08127302419202209</v>
+        <v>0.09405484177968049</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.07560128520998433</v>
+        <v>0.08681528246522419</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.01785521240336863</v>
+        <v>0.004288238118881793</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.01228367407009046</v>
+        <v>-0.001223274119780626</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1140614238366524</v>
+        <v>-0.1294108660193132</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.06652925056961578</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.001333126698703779</v>
+        <v>-0.01429237476062895</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0534046904311225</v>
+        <v>-0.06903942826353671</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.1255792850892874</v>
+        <v>-0.1420381169478944</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.08916431284205117</v>
+        <v>-0.1070561012376245</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1053440048849694</v>
+        <v>-0.1232667028220504</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1816768525302663</v>
+        <v>-0.2003793063515715</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.06389135604390361</v>
+        <v>-0.08411770781025751</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.0985533034347057</v>
+        <v>-0.119616784474232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02541</t>
+          <t>X &gt; -0.02542</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3958</v>
+        <v>3969</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.1518670801858448</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.06406916103657778</v>
+        <v>0.06395801284085678</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.01048098900128025</v>
+        <v>0.01046053882839004</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.003230667493205885</v>
+        <v>0.003249201163242788</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1180284144574841</v>
+        <v>-0.1203990368076973</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1346289411755421</v>
+        <v>-0.1355878722856616</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.07949997258621266</v>
+        <v>-0.08194868520151743</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.154388299956473</v>
+        <v>-0.1566991024695596</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2014933546394104</v>
+        <v>-0.2050095585549201</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2046153736615466</v>
+        <v>-0.2095750992542591</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1427536365744899</v>
+        <v>-0.1479171275004134</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2204658399348673</v>
+        <v>-0.2267392796246099</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.07077327293756497</v>
+        <v>-0.07885435204500624</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.03286482219804299</v>
+        <v>-0.04235089244749446</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02315</t>
+          <t>X &gt; -0.02316</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3920</v>
+        <v>3931</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1252370332846198</v>
+        <v>0.1268050108128165</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1805326678565535</v>
+        <v>0.1801069814103755</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1302722560833089</v>
+        <v>0.1299188144785859</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1217231365074056</v>
+        <v>0.1214158842933202</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.04637594280328727</v>
+        <v>-0.04943768337396648</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.04053741164705826</v>
+        <v>-0.04199947242132396</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.06042550799583779</v>
+        <v>-0.06341442223417459</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.1060418214872314</v>
+        <v>-0.1089853466646886</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.203955621049559</v>
+        <v>-0.2082061494035656</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2243620908180617</v>
+        <v>-0.2302739013014943</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.1854140311956911</v>
+        <v>-0.1914731636272293</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.238725952534601</v>
+        <v>-0.2462040708586386</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1345228550962858</v>
+        <v>-0.1439406682876339</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.0984514408778594</v>
+        <v>-0.1095083507934334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.02089</t>
+          <t>X &gt; -0.0209</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3853</v>
+        <v>3864</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.07987031193849248</v>
+        <v>0.0820986471274594</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1381695452245921</v>
+        <v>0.137877240627958</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.03552775265963959</v>
+        <v>-0.0354139951317336</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.08290638542929685</v>
+        <v>0.08271258942399129</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1305671255249692</v>
+        <v>-0.1342825222362762</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2075094981710777</v>
+        <v>-0.2089370577882548</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2263156982688415</v>
+        <v>-0.2297159397232207</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.2128308415245428</v>
+        <v>-0.2163743986520927</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.285493528879428</v>
+        <v>-0.2908544461630882</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.343365441227192</v>
+        <v>-0.350762082435196</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.326148321893271</v>
+        <v>-0.3336431210143687</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3550804687129201</v>
+        <v>-0.3645008549776207</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2417919119637091</v>
+        <v>-0.2536452318974582</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1830926163202591</v>
+        <v>-0.1970826724380785</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01863</t>
+          <t>X &gt; -0.01864</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3745</v>
+        <v>3756</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.04702436329214521</v>
+        <v>0.05024901353169042</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02022153889849676</v>
+        <v>0.02029920036056154</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1471503986620561</v>
+        <v>-0.1467030332128587</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1622409080404879</v>
+        <v>-0.1617100371747213</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3131584825915041</v>
+        <v>-0.3178395412554735</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.454211903146863</v>
+        <v>-0.4556468618475833</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3912294713722346</v>
+        <v>-0.3956231850306793</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5239096734697881</v>
+        <v>-0.5280591779011417</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5969917144678121</v>
+        <v>-0.6036991531238201</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.632129680353998</v>
+        <v>-0.6417475826662198</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5285522595950454</v>
+        <v>-0.5385405577532154</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5593632204655563</v>
+        <v>-0.5720112614717081</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.4040545960348183</v>
+        <v>-0.4200478521378699</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.296811158596725</v>
+        <v>-0.3158160944080635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01637</t>
+          <t>X &gt; -0.01638</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3628</v>
+        <v>3639</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.02280012830968303</v>
+        <v>-0.01832650177635742</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.136058167554225</v>
+        <v>-0.1354691346388321</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4335621590814398</v>
+        <v>-0.4322323778095978</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4534048243580386</v>
+        <v>-0.4519633559096476</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.59194094233127</v>
+        <v>-0.5974884893228491</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.8021843502716735</v>
+        <v>-0.8033843789193966</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6795232158547719</v>
+        <v>-0.6847288329006531</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8290346909481556</v>
+        <v>-0.8339773590629846</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9576413153486243</v>
+        <v>-0.965827542851315</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9666315093292397</v>
+        <v>-0.9787389563879074</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8532126972411049</v>
+        <v>-0.8657508598376538</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.8862142329559859</v>
+        <v>-0.9022561120068033</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6848868959643326</v>
+        <v>-0.7053248588681598</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.4988519538945297</v>
+        <v>-0.523387250687172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01411</t>
+          <t>X &gt; -0.01412</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3481</v>
+        <v>3492</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.134035664192055</v>
+        <v>-0.1278008405788498</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2129151782789691</v>
+        <v>-0.2120103712300576</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4777097053749841</v>
+        <v>-0.4761790536530057</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6471095506714732</v>
+        <v>-0.6449783797013993</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6829035339063978</v>
+        <v>-0.6904365567922994</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.000544685015385</v>
+        <v>-1.002177907847283</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9265403025375036</v>
+        <v>-0.933205123517034</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.9767016523910783</v>
+        <v>-0.9834572499824219</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.309005483830987</v>
+        <v>-1.319510031244214</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.454791907258702</v>
+        <v>-1.470049836914235</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.213280249233911</v>
+        <v>-1.229414648775958</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.249228922961521</v>
+        <v>-1.270007034960699</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.079207077272315</v>
+        <v>-1.10552085525655</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.8375071895777921</v>
+        <v>-0.8692490438424585</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01185</t>
+          <t>X &gt; -0.01186</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3323</v>
+        <v>3337</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2926666300547396</v>
+        <v>-0.2713058547377329</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2090436528335573</v>
+        <v>-0.1966033322584266</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6776353559836963</v>
+        <v>-0.6638488816311394</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7712898289112715</v>
+        <v>-0.7569038371249377</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.8733292744031687</v>
+        <v>-0.8714966006052407</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.160157703896438</v>
+        <v>-1.150587047287814</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.018610583827972</v>
+        <v>-1.015841515869731</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.139129614017932</v>
+        <v>-1.1365894958006</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.424267355493463</v>
+        <v>-1.426714856034614</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.536649013953671</v>
+        <v>-1.546050664301866</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.42429557364796</v>
+        <v>-1.434498044216838</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.373423992893017</v>
+        <v>-1.389889096932166</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.145302540894413</v>
+        <v>-1.169493703803937</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.963050063956338</v>
+        <v>-0.9937684299061047</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.009589</t>
+          <t>X &gt; -0.009598</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3135</v>
+        <v>3146</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.257281977167132</v>
+        <v>-0.2467373392902843</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.05470435876596724</v>
+        <v>0.05490615012182332</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5453604759310906</v>
+        <v>-0.5434095401060333</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5569663297887075</v>
+        <v>-0.5548614883215706</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5692381723134758</v>
+        <v>-0.5833175131502486</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.954547661690313</v>
+        <v>-0.9591486479505491</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.8948776847927178</v>
+        <v>-0.9076529903218074</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9946150975820913</v>
+        <v>-1.007455734976027</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.356821863087767</v>
+        <v>-1.376357052588261</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.616153369457543</v>
+        <v>-1.643436201376119</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.421095416667811</v>
+        <v>-1.449254178185797</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.305479186663227</v>
+        <v>-1.341940114649312</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9746972951860258</v>
+        <v>-1.020617288078604</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8906917819903768</v>
+        <v>-0.9446552579553327</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.007328</t>
+          <t>X &gt; -0.007338</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2936</v>
+        <v>2948</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4293731346374372</v>
+        <v>-0.4331108117157498</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1819820012322069</v>
+        <v>0.1634678467139139</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6015664163952934</v>
+        <v>-0.6174763745319254</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7585492473174753</v>
+        <v>-0.7398338645803193</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.769301245534578</v>
+        <v>-0.805133966305803</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.03098780126895</v>
+        <v>-1.055338549641206</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.859644278072679</v>
+        <v>-0.8948378646095989</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9005325581716406</v>
+        <v>-0.9362496958447153</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.317091453785508</v>
+        <v>-1.361246739240549</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.604461531205835</v>
+        <v>-1.624853158402829</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.41635704730443</v>
+        <v>-1.471712669524003</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.567530771070587</v>
+        <v>-1.59839565273645</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.117861046897119</v>
+        <v>-1.161234666253044</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.9072708814606329</v>
+        <v>-0.9612600913851281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.005067</t>
+          <t>X &gt; -0.005079</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2732</v>
+        <v>2743</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6776373420097599</v>
+        <v>-0.6596038423035324</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.1717462729032775</v>
+        <v>0.1716838667266671</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.7500889658814671</v>
+        <v>-0.7470123740292891</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.7461450824891429</v>
+        <v>-0.7429038451559435</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.9365285782035002</v>
+        <v>-0.9583106027459394</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.09391425318897</v>
+        <v>-1.102141557429249</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.013051903570492</v>
+        <v>-1.034262568501312</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.095288837224317</v>
+        <v>-1.116828686469226</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.392276089087233</v>
+        <v>-1.425277545008349</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.564629809043296</v>
+        <v>-1.610696300416336</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.456901126705645</v>
+        <v>-1.503711401915126</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.512205474761551</v>
+        <v>-1.571351103324567</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.034179101080717</v>
+        <v>-1.108442149740547</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8978956695209988</v>
+        <v>-0.9850284995349483</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.002807</t>
+          <t>X &gt; -0.002819</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2476</v>
+        <v>2487</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8537565287264002</v>
+        <v>-0.830111824886977</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1933882972316212</v>
+        <v>-0.1917282857931397</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.20983289717509</v>
+        <v>-1.204400797476836</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7766000944511049</v>
+        <v>-0.7728416957491859</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8909137729913397</v>
+        <v>-0.9201099468127296</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8133448866151625</v>
+        <v>-0.8261114892958901</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9166681258645681</v>
+        <v>-0.9454093207066023</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7577232297151184</v>
+        <v>-0.7880215222260105</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.119232746309812</v>
+        <v>-1.164355257443603</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.423147069937457</v>
+        <v>-1.484782508398865</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.404114022157238</v>
+        <v>-1.466241785649636</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.387951837929343</v>
+        <v>-1.466452390518278</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.8977907756141263</v>
+        <v>-0.9955972874042587</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.053415009504015</v>
+        <v>-1.1665337559606</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.000546</t>
+          <t>X &gt; -0.000559</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2196</v>
+        <v>2208</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.054931422114258</v>
+        <v>-1.001782243617285</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4236238627286113</v>
+        <v>-0.3995952163491481</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.8846986103015624</v>
+        <v>-0.9043319907414968</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.7755060256896087</v>
+        <v>-0.7953754991627022</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.108089845298196</v>
+        <v>-1.125147072519674</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5594513655394451</v>
+        <v>-0.5573609919112315</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.891988273819365</v>
+        <v>-0.9096576023613565</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6080168240667447</v>
+        <v>-0.6285506134375041</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.9168220945980607</v>
+        <v>-0.9572215756174813</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.969334753221915</v>
+        <v>-1.033229249397017</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8761319055289931</v>
+        <v>-0.9411563693575999</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8620500165508957</v>
+        <v>-0.9937480570619286</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.483216565433942</v>
+        <v>-0.6396469876221644</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7783518163285876</v>
+        <v>-0.9540702500778337</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001715</t>
+          <t>X &gt; 0.001701</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1939</v>
+        <v>1950</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.251407833813047</v>
+        <v>-1.211079731152907</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9911282640389842</v>
+        <v>-0.9842165349154186</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.820206841686556</v>
+        <v>-1.809821390963357</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.022117836288714</v>
+        <v>-2.010204081632665</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.071529293630569</v>
+        <v>-2.115406801565932</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.02796964066512</v>
+        <v>-1.049602393474018</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.804576405765012</v>
+        <v>-1.849387760121132</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.678905873283519</v>
+        <v>-1.725862200050294</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.918143977842306</v>
+        <v>-1.991287886870559</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.917166129257097</v>
+        <v>-2.020261923135301</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.733534085810355</v>
+        <v>-1.838360059050459</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.722581275589718</v>
+        <v>-1.854821048679767</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.289892961081243</v>
+        <v>-1.453335177611436</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.809200722539977</v>
+        <v>-1.996573037145829</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.003975</t>
+          <t>X &gt; 0.003961</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1682</v>
+        <v>1693</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.005119100191962</v>
+        <v>-0.9274623524368124</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.050164734348328</v>
+        <v>-1.014110024412339</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.063705659653458</v>
+        <v>-2.022238165963181</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.316435472984843</v>
+        <v>-2.272586192433522</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.113872829103158</v>
+        <v>-2.143689295392086</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.133975966378223</v>
+        <v>-1.134453040122409</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.95715576407931</v>
+        <v>-1.9872037449719</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.563095114159225</v>
+        <v>-1.598035293569765</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.7426309162066</v>
+        <v>-1.780177478657492</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.027029134759715</v>
+        <v>-2.101144014416867</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.843580017228</v>
+        <v>-1.919753947504596</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.420590603005003</v>
+        <v>-1.534598842576948</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.8574913218876077</v>
+        <v>-1.012063574697784</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.193115227914667</v>
+        <v>-1.439043541636423</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.006236</t>
+          <t>X &gt; 0.00622</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2317810824374646</v>
+        <v>-0.1454785144003523</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.3524899352325335</v>
+        <v>-0.3209981007149878</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.333720355200064</v>
+        <v>-1.295537536655416</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.414900791949329</v>
+        <v>-2.434065934065934</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.570163455681502</v>
+        <v>-2.612715022149757</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.403119443781023</v>
+        <v>-1.409920096882459</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.215283281543051</v>
+        <v>-2.191041646271444</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.950455547745683</v>
+        <v>-1.932051251749662</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.011437704268459</v>
+        <v>-2.070217490054532</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.444110325354934</v>
+        <v>-2.512620656767474</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.67523707471387</v>
+        <v>-1.713691210678945</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.432235834736851</v>
+        <v>-1.479798405803216</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.296058454392401</v>
+        <v>-1.353444879828544</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.626651037823727</v>
+        <v>-1.757824234081681</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.008497</t>
+          <t>X &gt; 0.00848</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1201</v>
+        <v>1210</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4113796066932949</v>
+        <v>-0.1797765836768477</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6538254044598233</v>
+        <v>-0.492634245558385</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.418880141852391</v>
+        <v>-1.251973663304312</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.489428447752402</v>
+        <v>-2.389929742388766</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.071017652079817</v>
+        <v>-2.098237773320378</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8984782689403374</v>
+        <v>-0.8790251984876747</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.520876576942555</v>
+        <v>-1.552914992494735</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.194305422502346</v>
+        <v>-1.234963749937286</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.671607312580498</v>
+        <v>-1.721430077939139</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.688054002332507</v>
+        <v>-2.74837592575571</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.22664358690411</v>
+        <v>-2.249126001821821</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.859209647704482</v>
+        <v>-1.898949436928419</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.446721033907153</v>
+        <v>-1.50615697472918</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.136888797502436</v>
+        <v>-2.120751888597418</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.01076</t>
+          <t>X &gt; 0.01074</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9199895451365663</v>
+        <v>-0.7722766709644446</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.571940833275605</v>
+        <v>-1.608199446822155</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.216439603206901</v>
+        <v>-2.248220928208291</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.144527152643647</v>
+        <v>-3.062322140011389</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.822137108962671</v>
+        <v>-3.001925397895377</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.45991206636311</v>
+        <v>-1.579594503227945</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.80790747950784</v>
+        <v>-2.78611072034947</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.019525447059308</v>
+        <v>-3.100095328884656</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.486187116766665</v>
+        <v>-3.585516386469898</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-4.234686034800383</v>
+        <v>-4.357690106010779</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.323768531802962</v>
+        <v>-3.406762141899108</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.985130744559207</v>
+        <v>-2.994420429810837</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.69534244979959</v>
+        <v>-2.833686447028747</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-3.788065217422954</v>
+        <v>-3.83849637202691</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.01302</t>
+          <t>X &gt; 0.013</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.300791806931869</v>
+        <v>-1.212213184590325</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.59956481016534</v>
+        <v>-2.671780875432205</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.805677991541266</v>
+        <v>-2.941909469432936</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.359142130350889</v>
+        <v>-3.430072399788102</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.085949153815612</v>
+        <v>-2.371144473342305</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8475638882254657</v>
+        <v>-1.108259944622382</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.991410668017288</v>
+        <v>-2.282777419986459</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.083009975133187</v>
+        <v>-2.311991239665325</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.393053458314292</v>
+        <v>-1.605469425010305</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.242972254644151</v>
+        <v>-2.429298005825288</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.321265402891825</v>
+        <v>-1.450396767861356</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.161730804979555</v>
+        <v>-1.324261533355461</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.7057865393943388</v>
+        <v>-0.9050132301983282</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.481302453623378</v>
+        <v>-1.58299574685622</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01528</t>
+          <t>X &gt; 0.01526</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.02079333114785</v>
+        <v>-2.051396228556712</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.632808728820919</v>
+        <v>-2.717142121052007</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.717642739122454</v>
+        <v>-3.875406103250505</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.509190737646215</v>
+        <v>-3.745522062035825</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.580123103045736</v>
+        <v>-2.932150037911008</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.201891554376935</v>
+        <v>-2.65936451909208</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.753481677832191</v>
+        <v>-4.251414176464564</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-3.601355275179309</v>
+        <v>-3.951550152774395</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.817136193311981</v>
+        <v>-4.141662118725897</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.512256228031944</v>
+        <v>-4.812351342726174</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.168969770193058</v>
+        <v>-3.33195886530055</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.289390379447639</v>
+        <v>-3.499508265817454</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.935547424711515</v>
+        <v>-3.199416788443962</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-4.103000628974144</v>
+        <v>-4.252983293556092</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01754</t>
+          <t>X &gt; 0.01752</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.189653894612022</v>
+        <v>-2.316313375274582</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.535681890135152</v>
+        <v>-2.736699762756011</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-4.194475847534513</v>
+        <v>-4.487026898357541</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.089591834550433</v>
+        <v>-3.388150609080846</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.355875417860553</v>
+        <v>-2.714609052358341</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.325548232648167</v>
+        <v>-3.798412680826239</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.074431110236731</v>
+        <v>-5.603254816563329</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.345421322650921</v>
+        <v>-5.681490677721868</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-4.818168185056052</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.275930118640815</v>
+        <v>-5.573299619611632</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.108082257293155</v>
+        <v>-4.227052470248495</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.485468810820187</v>
+        <v>-3.679685762988214</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.317384370015951</v>
+        <v>-3.583740217828264</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.875962445279612</v>
+        <v>-4.011267893945956</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.0198</t>
+          <t>X &gt; 0.01978</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.616718499670156</v>
+        <v>-1.89886488112171</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5118552100179414</v>
+        <v>-0.7925554137103177</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-3.375762397242113</v>
+        <v>-3.631281177086144</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.751710093159922</v>
+        <v>-3.012399580859238</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.79617248576178</v>
+        <v>-3.012651166798939</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.745712036373618</v>
+        <v>-3.22886320299223</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.571163136380527</v>
+        <v>-4.02301562473604</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.803663878932689</v>
+        <v>-3.021855720082698</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.358473195949301</v>
+        <v>-3.54782588423172</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.714564831785324</v>
+        <v>-3.638158132528368</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.931611669057865</v>
+        <v>-2.864303470040007</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.403406356208713</v>
+        <v>-2.185301601556652</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.823557209522122</v>
+        <v>-2.335361488904795</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.585475880283255</v>
+        <v>-3.066708783752169</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.02206</t>
+          <t>X &gt; 0.02204</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>322</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.859798018111988</v>
+        <v>-2.045715540057259</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.918189080119923</v>
+        <v>-2.080905009114041</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-4.797432514564399</v>
+        <v>-4.951423183187259</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.735530352342494</v>
+        <v>-3.892746572313136</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-5.001190759704691</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.423650844747208</v>
+        <v>-2.561222578347056</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.508361204013376</v>
+        <v>-2.621878667572517</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4909577981106708</v>
+        <v>-0.3013337189775385</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.794175979478169</v>
+        <v>-1.576696420993592</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.33353576959685</v>
+        <v>-2.090927478588753</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.29600090301232</v>
+        <v>-1.056677833245587</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.882740763079362</v>
+        <v>-1.759044142051117</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.924009628815128</v>
+        <v>-2.7753200810373</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.251069009644496</v>
+        <v>-4.079070250077834</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.02432</t>
+          <t>X &gt; 0.0243</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>241</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.6311171644863975</v>
+        <v>0.6019213701337662</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.395006687913529</v>
+        <v>-1.396193474358185</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.034591350676877</v>
+        <v>-3.034744740681198</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.489428447752402</v>
+        <v>-2.489922940130405</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.932282316200805</v>
+        <v>-5.883736396435033</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.56021948988522</v>
+        <v>-3.536262080935607</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.229992089815291</v>
+        <v>-3.18198041082497</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.7924964182493284</v>
+        <v>-0.7432488558556116</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.928167371452595</v>
+        <v>-2.854910261672899</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.193023927118553</v>
+        <v>-4.093676601823979</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.737974048034353</v>
+        <v>-2.638066012015678</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-5.193222451695632</v>
+        <v>-5.069525830667388</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-5.613373305009041</v>
+        <v>-5.464683757231214</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-7.047388692126901</v>
+        <v>-6.875389932560239</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.02658</t>
+          <t>X &gt; 0.02656</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.492056942438623</v>
+        <v>0.1780602181237683</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5785886100846724</v>
+        <v>-0.8674824584299401</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.054441075920792</v>
+        <v>-2.336489263948941</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.005297013413511</v>
+        <v>-3.281874039938558</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-6.2462892692119</v>
+        <v>-6.459295223901229</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.327293617955199</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-2.790382355599739</v>
+        <v>-3.021359342694865</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.095288837224317</v>
+        <v>-1.336654468669607</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.318433155909254</v>
+        <v>-3.524164712215004</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.62781141169858</v>
+        <v>-3.810358884427835</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.832512569958773</v>
+        <v>-4.014499331963925</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.338674958143983</v>
+        <v>-4.493967003201185</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.299366351997939</v>
+        <v>-5.426759338367155</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-6.154711782852488</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02884</t>
+          <t>X &gt; 0.02882</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>137</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.263609516910904</v>
+        <v>2.234413722558273</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.6524234238470754</v>
+        <v>0.6512366374024197</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4722749682072376</v>
+        <v>-0.4724283582115589</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-2.531830846516677</v>
+        <v>-2.53232533889468</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-8.909536458006535</v>
+        <v>-8.860990538240763</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-9.342089435670722</v>
+        <v>-9.318132026721109</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.317310743841993</v>
+        <v>-4.269299064851673</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-4.784379387628732</v>
+        <v>-4.735131825235015</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.305215558750049</v>
+        <v>-6.231958448970353</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-6.425207347780642</v>
+        <v>-6.325860022486069</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.170054491442293</v>
+        <v>-5.070146455423618</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-6.595530353685511</v>
+        <v>-6.471833732657267</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-7.745608214298187</v>
+        <v>-7.596918666520359</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-6.789945556772388</v>
+        <v>-6.617946797205725</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.0311</t>
+          <t>X &gt; 0.03108</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>104</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.4036993540810343</v>
+        <v>0.374503559728403</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.7155901840941326</v>
+        <v>0.7144033976494768</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.3208187993390936</v>
+        <v>0.3206654093347723</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-9.702630225552859</v>
+        <v>-9.654084305787087</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-11.32833311899469</v>
+        <v>-11.30437571004508</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-5.643812709030101</v>
+        <v>-5.59580103003978</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-4.187804429739913</v>
+        <v>-4.138556867346196</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4.248786586262689</v>
+        <v>-4.175529476482993</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-3.175628459515622</v>
+        <v>-3.076281134221048</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-2.418791156237354</v>
+        <v>-2.318883120218679</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-4.307489926958951</v>
+        <v>-4.183793305930706</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-7.386520514661221</v>
+        <v>-7.214521755094559</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.03336</t>
+          <t>X &gt; 0.03334</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.5206735521696118</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.105921127400833</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-6.737600745717245</v>
+        <v>-6.738095238095248</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-12.0377950607177</v>
+        <v>-11.98924914095193</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-12.93089722155879</v>
+        <v>-12.90693981260918</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-6.339819081754563</v>
+        <v>-6.290571519360846</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-2.829372666848762</v>
+        <v>-2.756115557069066</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1078628917500524</v>
+        <v>-0.008515566455479018</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>-0.2126560139915696</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-2.659138278607308</v>
+        <v>-2.535441657579064</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-4.2697653223969</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
   </sheetData>
@@ -3911,1554 +3911,1554 @@
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.083325669088573</v>
+        <v>-3.112521463441205</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.080053930827091</v>
+        <v>-1.081240717271747</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.344451792851594</v>
+        <v>3.344298402847272</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>3.474676936439955</v>
+        <v>3.474182444061952</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.755664491778006</v>
+        <v>7.804210411543778</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.46267707562995</v>
+        <v>10.48663448457957</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.173147439255345</v>
+        <v>9.221159118245666</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.910898072577048</v>
+        <v>9.960145634970765</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12.25955447027114</v>
+        <v>12.33281158005084</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>12.61445495104971</v>
+        <v>12.71380227634428</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>12.40975379278952</v>
+        <v>12.50966182880819</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.64895122225328</v>
+        <v>13.77264784328153</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>12.02398109183143</v>
+        <v>12.17267063960926</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.04489746494954</v>
+        <v>11.2168962245162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02993</t>
+          <t>X &lt; -0.02994</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>111</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.6722371226188031</v>
+        <v>0.6430413282661718</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.8628528313567756</v>
+        <v>0.8616660449121198</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.4680814466017367</v>
+        <v>0.4679280565974153</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.5983065901900986</v>
+        <v>0.5978120978120955</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.465422442499815</v>
+        <v>5.513968362265587</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>8.465499174837596</v>
+        <v>8.489456583787209</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.479887914670527</v>
+        <v>7.527899593660848</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.111918369982881</v>
+        <v>6.161165932376598</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.654539817063721</v>
+        <v>9.727796926843418</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.903720119832954</v>
+        <v>8.003067445127527</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>8.599919862473669</v>
+        <v>8.699827898492345</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.313246260614676</v>
+        <v>7.461935808392504</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.538981910841208</v>
+        <v>7.710980670407871</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02767</t>
+          <t>X &lt; -0.02768</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.149790202719778</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4497180176379203</v>
+        <v>-0.7599555767095012</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.8444894023929592</v>
+        <v>-0.4870268983575414</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.05201260317545575</v>
+        <v>0.3095238095238031</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.383207777503685</v>
+        <v>3.820274668571884</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.356078495880496</v>
+        <v>2.759726854057483</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.609116480985186</v>
+        <v>2.032404098165351</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.466551148456723</v>
+        <v>2.899904671115337</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.716827270079648</v>
+        <v>6.196265395311876</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.866908473749788</v>
+        <v>5.372436814496893</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>4.662207315489596</v>
+        <v>5.168296366960803</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6.683340434732337</v>
+        <v>7.226463104325695</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.614182958902369</v>
+        <v>4.164638511095212</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.502170264758043</v>
+        <v>5.080350039777237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02541</t>
+          <t>X &lt; -0.02542</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>200</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.980916030534353</v>
+        <v>-3.010111824886984</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.09210212359818115</v>
+        <v>-0.0932889100428369</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4868735083532201</v>
+        <v>-0.4870268983575414</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1433516352351489</v>
+        <v>0.1428571428571459</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.60506208213944</v>
+        <v>2.653608001905212</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.402436111774527</v>
+        <v>3.42639352072414</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.817725752508359</v>
+        <v>2.86573743149868</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.850657108721627</v>
+        <v>3.899904671115344</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.789674952198851</v>
+        <v>5.862932061978547</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.939756155868992</v>
+        <v>6.039103481163565</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.235054997608799</v>
+        <v>4.334963033627474</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.769433149964122</v>
+        <v>5.893129770992367</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.849282296650713</v>
+        <v>2.997971844428541</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.075017946877246</v>
+        <v>2.247016706443908</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02315</t>
+          <t>X &lt; -0.02316</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>238</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.060747963307463</v>
+        <v>-2.089943757660095</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.991261787463721</v>
+        <v>-1.992448573908376</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.38603317221876</v>
+        <v>-2.386186562223081</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.835639961403508</v>
+        <v>-1.836134453781511</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.9874150233159185</v>
+        <v>1.03596094308169</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.284789052951005</v>
+        <v>1.308746461900618</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.040414828138616</v>
+        <v>2.088426507128936</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.413682318805655</v>
+        <v>2.462929881199372</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.873708565644229</v>
+        <v>4.946965675423925</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.284293970995044</v>
+        <v>5.383641296289618</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>4.239256678281066</v>
+        <v>4.339164714299741</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.113970965090175</v>
+        <v>5.23766758611842</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>3.433315910096091</v>
+        <v>3.582005457873919</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.818715425868845</v>
+        <v>2.990714185435507</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.02089</t>
+          <t>X &lt; -0.0209</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>305</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.005506194468772</v>
+        <v>-1.034701988821404</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9773480252375322</v>
+        <v>-0.9785348116821879</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2672248523025118</v>
+        <v>0.2670714622981905</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.9140254139451827</v>
+        <v>-0.9145199063231857</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.826373557549289</v>
+        <v>1.874919477315061</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.107354144561427</v>
+        <v>3.13131155351104</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.678381490213283</v>
+        <v>3.726393169203604</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.211312846426544</v>
+        <v>3.260560408820261</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.579100418164074</v>
+        <v>5.678447743458648</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.04653040744487</v>
+        <v>5.146438443463545</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.408777412259205</v>
+        <v>5.53247403328745</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.005020001568745</v>
+        <v>4.153709549346573</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.247149094418234</v>
+        <v>3.419147853984896</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01863</t>
+          <t>X &lt; -0.01864</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>413</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4228046503890752</v>
+        <v>-0.4520004447417065</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3873167626003706</v>
+        <v>0.3861299761557149</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.203199130871965</v>
+        <v>1.203045740867644</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.575555025065647</v>
+        <v>1.575060532687644</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.974311476812574</v>
+        <v>3.022857396578345</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.482339259474287</v>
+        <v>4.5062966684239</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.155498149602799</v>
+        <v>4.20350982859312</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.141214009448014</v>
+        <v>5.19046157184173</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.290885605951878</v>
+        <v>6.364142715731575</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.651620562648652</v>
+        <v>6.750967887943226</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.478396401967153</v>
+        <v>5.578304437985828</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.754905304927803</v>
+        <v>5.878601925956048</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.366231449193087</v>
+        <v>4.514920996970915</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.381313346392986</v>
+        <v>3.553312105959648</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01637</t>
+          <t>X &lt; -0.01638</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>530</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1605934034279102</v>
+        <v>0.1313976090752789</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.379595989609363</v>
+        <v>1.378409203164708</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.871617057684517</v>
+        <v>2.871463667680196</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.190521446555898</v>
+        <v>3.190026954177895</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.161665855724351</v>
+        <v>4.210211775490123</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.779794602340573</v>
+        <v>5.803752011290186</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.129046507225347</v>
+        <v>5.177058186215667</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.982732580419736</v>
+        <v>6.031980142813453</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7.242505140878094</v>
+        <v>7.315762250657791</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.335982570963331</v>
+        <v>7.435329896257905</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.376564431571062</v>
+        <v>6.476472467589737</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.599621829209404</v>
+        <v>6.723318450237649</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.236074749480899</v>
+        <v>5.384764297258727</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.952376437443284</v>
+        <v>4.124375197009947</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01411</t>
+          <t>X &lt; -0.01412</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>677</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6948594495247349</v>
+        <v>0.6656636551721036</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.447041155574638</v>
+        <v>1.445854369129982</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.381664157821085</v>
+        <v>2.381510767816764</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.398152226077087</v>
+        <v>3.397657733699084</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.598415110204435</v>
+        <v>3.646961029970207</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.372894014285613</v>
+        <v>5.396851423235226</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.140473167574832</v>
+        <v>5.188484846565153</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.26424647356653</v>
+        <v>5.313494035960247</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7.271211141268267</v>
+        <v>7.344468251047964</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>8.046107706829105</v>
+        <v>8.145455032123678</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>6.659722649012053</v>
+        <v>6.759630685030729</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.841811288811982</v>
+        <v>6.965507909840227</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.978528973164742</v>
+        <v>6.12721852094257</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.727159748945198</v>
+        <v>4.89915850851186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01185</t>
+          <t>X &lt; -0.01186</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.171778580244087</v>
+        <v>1.095657405882243</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.117478714725173</v>
+        <v>1.074980320726389</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.638874994640794</v>
+        <v>2.604319255488612</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.128381575354901</v>
+        <v>3.094780219780212</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.54817585459454</v>
+        <v>3.567069540366759</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.80363371656496</v>
+        <v>4.801393520724147</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4.359641920173033</v>
+        <v>4.38016050842176</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.730896629679705</v>
+        <v>4.75567390188457</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>6.107040221659929</v>
+        <v>6.161008985055474</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>6.574486694791148</v>
+        <v>6.659295788855879</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>6.01050409940521</v>
+        <v>6.094578418242861</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.80536129367669</v>
+        <v>5.912360540223141</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.906168524195621</v>
+        <v>5.036433382890081</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.173820342086827</v>
+        <v>4.323939783366981</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.009589</t>
+          <t>X &lt; -0.009598</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1023</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7937662764060178</v>
+        <v>0.7645704820533865</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.06234557923661299</v>
+        <v>0.06115879279195724</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.622608407580302</v>
+        <v>1.62245501757598</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.752833551168663</v>
+        <v>1.75233905879066</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.801054262002602</v>
+        <v>1.849600181768373</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.075945398187052</v>
+        <v>3.099902807136665</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.991235038920884</v>
+        <v>3.039246717911205</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.208428369718696</v>
+        <v>3.257675932112413</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.515970162365029</v>
+        <v>4.589227272144726</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.327830447169092</v>
+        <v>5.427177772463665</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.634370735634214</v>
+        <v>4.734278771652889</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.277742045369791</v>
+        <v>4.401438666398036</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.271080928126764</v>
+        <v>3.419770475904592</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.008058025078618</v>
+        <v>3.180056784645281</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.007328</t>
+          <t>X &lt; -0.007338</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.037905573393637</v>
+        <v>1.052541737766575</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.2030350197889419</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.40510685171224</v>
+        <v>1.450729039398396</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.862664237526467</v>
+        <v>1.826313326313318</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.897206108326024</v>
+        <v>1.992264840562065</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.603745440743445</v>
+        <v>2.674550768881396</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.273535899807882</v>
+        <v>2.368194433955694</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.297465619359933</v>
+        <v>2.393762164972834</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.463979371184116</v>
+        <v>3.585290784337275</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.168888725427088</v>
+        <v>4.235663677723764</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.636855324941045</v>
+        <v>3.785822984487424</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.998565719522219</v>
+        <v>4.089689967552566</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.923750381757095</v>
+        <v>3.039331385788081</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.412988486975443</v>
+        <v>2.551275510702709</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.005067</t>
+          <t>X &lt; -0.005079</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1426</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.305900238750354</v>
+        <v>1.276704444397723</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1650333998955134</v>
+        <v>-0.1662201863401691</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.403729577200785</v>
+        <v>1.403576187196464</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.463828493580166</v>
+        <v>1.463334001202163</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.837179894201157</v>
+        <v>1.885725813966928</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.204680151045224</v>
+        <v>2.228637559994837</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.119969791779056</v>
+        <v>2.167981470769377</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.213910965664127</v>
+        <v>2.263158528057843</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.924317308440088</v>
+        <v>2.997574418219784</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.266544374662814</v>
+        <v>3.365891699957388</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.991716989193655</v>
+        <v>3.091625025212331</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.096221368757945</v>
+        <v>3.21991798978619</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.185186924981707</v>
+        <v>2.333876472759535</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.92003898474541</v>
+        <v>2.092037744312073</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.002807</t>
+          <t>X &lt; -0.002819</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1682</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.264624992057797</v>
+        <v>1.235429197705166</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4263283163542582</v>
+        <v>0.4251415299096024</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.755694862633703</v>
+        <v>1.755541472629382</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.172483620966418</v>
+        <v>1.171989128588415</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.347630453126371</v>
+        <v>1.396176372892143</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.288286290133634</v>
+        <v>1.312243699083247</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.500841091390647</v>
+        <v>1.548852770380968</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.21213154391782</v>
+        <v>1.261379106311537</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.864585772650692</v>
+        <v>1.937842882430388</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.32263368262285</v>
+        <v>2.421981007917424</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.236838588571942</v>
+        <v>2.336746624590617</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.211763708822623</v>
+        <v>2.335460329850868</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.494347694986033</v>
+        <v>1.64303724276386</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.720083345212565</v>
+        <v>1.892082104779227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.000546</t>
+          <t>X &lt; -0.000559</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.188808740107852</v>
+        <v>1.135987104230821</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5969906388890749</v>
+        <v>0.5726978314156028</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9667452480178298</v>
+        <v>0.9948700929734144</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8930967932371843</v>
+        <v>0.9207765717199621</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.272238432802034</v>
+        <v>1.298432071257594</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7031496693688268</v>
+        <v>0.7043129495869707</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.128123306025188</v>
+        <v>1.153600766531838</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7629914614229492</v>
+        <v>0.7897567873825579</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.211693300822702</v>
+        <v>1.262728084416082</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.279205697153394</v>
+        <v>1.356798534707679</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.125472938485458</v>
+        <v>1.203652477788623</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.108882691248525</v>
+        <v>1.261819215153515</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6887318379351157</v>
+        <v>0.8666612885896896</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.016404287346163</v>
+        <v>1.217694931839119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001715</t>
+          <t>X &lt; 0.001701</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2219</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.101778877081692</v>
+        <v>1.072583082729061</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.977749160764148</v>
+        <v>0.9765623743194922</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.574415360506627</v>
+        <v>1.574261970502306</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.794771193594755</v>
+        <v>1.794276701216752</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.8423311222476</v>
+        <v>1.890877042013372</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9680061883856155</v>
+        <v>0.9919635973352285</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.694472034617426</v>
+        <v>1.742483713607747</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.542860804079893</v>
+        <v>1.59210836647361</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.842401405556224</v>
+        <v>1.91565851533592</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.848724159474223</v>
+        <v>1.948071484768796</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.64402300121403</v>
+        <v>1.743931037232706</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.63333580881946</v>
+        <v>1.757032429847705</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.258250300255945</v>
+        <v>1.406939848033772</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.70931267423191</v>
+        <v>1.881311433798572</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.003975</t>
+          <t>X &lt; 0.003961</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2476</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6882402068495779</v>
+        <v>0.6401305014458103</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8130250463654818</v>
+        <v>0.7936254679862458</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.387167670492161</v>
+        <v>1.369192810850855</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.598135648153999</v>
+        <v>1.579852296330486</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.463560265425677</v>
+        <v>1.494480376703272</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8323917032157908</v>
+        <v>0.8383482864753589</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.433995433574168</v>
+        <v>1.464283473501915</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.128412457934381</v>
+        <v>1.160001601648467</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.332485937659271</v>
+        <v>1.365355325306496</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.532647916773676</v>
+        <v>1.591607519935778</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.368334480645956</v>
+        <v>1.427854794532159</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.079610855941503</v>
+        <v>1.162919754837276</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6998477247605734</v>
+        <v>0.808149550405922</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9255833749871059</v>
+        <v>1.097582134553768</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.006236</t>
+          <t>X &lt; 0.00622</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2720</v>
+        <v>2723</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1236327589007189</v>
+        <v>0.0789443631409199</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2732683826380651</v>
+        <v>0.2585289379189675</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.6855402847502248</v>
+        <v>0.6727233770739645</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.292654643305568</v>
+        <v>1.316746235769372</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.377989448243632</v>
+        <v>1.415084314795408</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.7949526194781242</v>
+        <v>0.8064890036473855</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.260499046712326</v>
+        <v>1.259971731902652</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.086900689059114</v>
+        <v>1.087932581508291</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.193344676969495</v>
+        <v>1.234580978614609</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.428742940009961</v>
+        <v>1.475754234009692</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.988084744211811</v>
+        <v>1.014544377733245</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.8598078744314321</v>
+        <v>0.8890901088550152</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.7913991654489436</v>
+        <v>0.8244499935287948</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.9647238292301807</v>
+        <v>1.036770654295537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.008497</t>
+          <t>X &lt; 0.00848</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2957</v>
+        <v>2959</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1684258526921099</v>
+        <v>0.07522105784367028</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3459674005327713</v>
+        <v>0.2831896300044789</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.5586884221226498</v>
+        <v>0.4977652611558128</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.026409347013747</v>
+        <v>0.999396514266401</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8593651533510567</v>
+        <v>0.8818945852103965</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4142484641201278</v>
+        <v>0.4111856802375016</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.700783464286971</v>
+        <v>0.7222768029079489</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5374610236726909</v>
+        <v>0.5606008522576218</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7991280244473344</v>
+        <v>0.8277850528538409</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.217702795517759</v>
+        <v>1.254378912052374</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.9985685111223077</v>
+        <v>1.016443263434844</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.8495277765271467</v>
+        <v>0.8718387943110528</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6853201600719458</v>
+        <v>0.7132472753173502</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.9642638041650429</v>
+        <v>0.9622921373327173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.01076</t>
+          <t>X &lt; 0.01074</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3172</v>
+        <v>3175</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.2881210997362587</v>
+        <v>0.2457936869240385</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.5649148682205691</v>
+        <v>0.583876444287867</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6736047798783744</v>
+        <v>0.6940754638471844</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.9926279096215467</v>
+        <v>0.9814398200224872</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8948669908870883</v>
+        <v>0.9646316239524566</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.4999817379545206</v>
+        <v>0.5445037569446214</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.9501990061269936</v>
+        <v>0.9562886126010497</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.9865916587530918</v>
+        <v>1.025888923083855</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.19508886469491</v>
+        <v>1.240884817884059</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.433458926649841</v>
+        <v>1.487922378801365</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.120881769262347</v>
+        <v>1.15779767929677</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.015809961558325</v>
+        <v>1.0269880387089</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.9288599833825089</v>
+        <v>0.9782868050584597</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.267325639184932</v>
+        <v>1.290323793058079</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.01302</t>
+          <t>X &lt; 0.013</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3359</v>
+        <v>3366</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.3117161738625498</v>
+        <v>0.2915484182200458</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6910232477624803</v>
+        <v>0.7109815525906171</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.652758101866624</v>
+        <v>0.6894785896282229</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.8126920986932475</v>
+        <v>0.8357354811360693</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.5120733715036749</v>
+        <v>0.583875064219761</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2449791896117262</v>
+        <v>0.3091480472898951</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5464839224430094</v>
+        <v>0.62108184955094</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.5415932157052836</v>
+        <v>0.6006172601889759</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.4377130021394038</v>
+        <v>0.4910876901341794</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.645078784474407</v>
+        <v>0.6938866065349174</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.3977557709579926</v>
+        <v>0.4303284525223035</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.3597336557659716</v>
+        <v>0.399368630172404</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2540442014126185</v>
+        <v>0.3012992359912303</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.4371793044241414</v>
+        <v>0.4612175382918053</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01528</t>
+          <t>X &lt; 0.01526</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3512</v>
+        <v>3519</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.3750089481527752</v>
+        <v>0.3810446376980465</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.5541041850122213</v>
+        <v>0.5707315039066927</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6708417516638292</v>
+        <v>0.7029901180916909</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.6589810754170102</v>
+        <v>0.7066869300911804</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4901146538927819</v>
+        <v>0.5578633210541497</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4464827159234446</v>
+        <v>0.5342255298047434</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.7596126521957771</v>
+        <v>0.858215433201778</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.706256881319689</v>
+        <v>0.7772470901954094</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.8033229476495194</v>
+        <v>0.8697483073633876</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9363431865857166</v>
+        <v>0.9993307538908383</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6625087671678358</v>
+        <v>0.6977081316666869</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.6846295073915556</v>
+        <v>0.7274577050645519</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6222683484582845</v>
+        <v>0.6733057461051573</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.8358379924353372</v>
+        <v>0.8655162801864478</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01754</t>
+          <t>X &lt; 0.01752</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3648</v>
+        <v>3656</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3090183239514275</v>
+        <v>0.326767607737132</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4210269792464558</v>
+        <v>0.4496851690840344</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.5733015463513738</v>
+        <v>0.6166848920354795</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4449932221024397</v>
+        <v>0.4886119886119857</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3444601669547609</v>
+        <v>0.396644593931434</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.5050352909811053</v>
+        <v>0.5752599506613194</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7760020862976944</v>
+        <v>0.8575407101872088</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.7893544267292825</v>
+        <v>0.8441517331541561</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7710601150786758</v>
+        <v>0.8224727946193369</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.840084742944569</v>
+        <v>0.8889804294818546</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.6509684459791103</v>
+        <v>0.6730374318769208</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.5639536979093265</v>
+        <v>0.5944426812768313</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.5430340094487391</v>
+        <v>0.5822169210149752</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.6199740872281225</v>
+        <v>0.6397956998793504</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.0198</t>
+          <t>X &lt; 0.01978</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3753</v>
+        <v>3761</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.174421197293583</v>
+        <v>0.2065592591310335</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1177252336395327</v>
+        <v>0.1484926382074292</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3484081069496483</v>
+        <v>0.3790563686803807</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3071836841322977</v>
+        <v>0.337817355058732</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.3150567658183476</v>
+        <v>0.3406602704114476</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3346349950502656</v>
+        <v>0.3892385313398634</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4507044759126231</v>
+        <v>0.5024509966699142</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.3441394178463923</v>
+        <v>0.3698993604408827</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.457583414146697</v>
+        <v>0.4804619424566354</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.5008421287196683</v>
+        <v>0.4950014620349847</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3910720370124139</v>
+        <v>0.3855875353548157</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.3340137092184534</v>
+        <v>0.310881564773922</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3817809647380841</v>
+        <v>0.3294444653748485</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.4628410217506769</v>
+        <v>0.4074793493580273</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.02206</t>
+          <t>X &lt; 0.02204</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3836</v>
+        <v>3847</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1561325535134515</v>
+        <v>0.1719301549005223</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2218271903311262</v>
+        <v>0.2353787934304634</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3870542275448798</v>
+        <v>0.4001911467552404</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3235388427234369</v>
+        <v>0.3368405453467744</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.4236576608130491</v>
+        <v>0.432466627067349</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2411457891938866</v>
+        <v>0.2525481652493156</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2747905456387372</v>
+        <v>0.2839829544677954</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.08230729091839351</v>
+        <v>0.06605212698243434</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2439837259556867</v>
+        <v>0.2251756350764396</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2939228225356629</v>
+        <v>0.2728697149297972</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.182046401620255</v>
+        <v>0.1612815579194944</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2311319514232153</v>
+        <v>0.219448295284387</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3208746865386516</v>
+        <v>0.3067036531603478</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.4311180511525308</v>
+        <v>0.4145498491525146</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.02432</t>
+          <t>X &lt; 0.0243</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3917</v>
+        <v>3928</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.0381679389313021</v>
+        <v>-0.03612045213895243</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1456173979085662</v>
+        <v>0.1452897701602041</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1719859621152153</v>
+        <v>0.1715158789971127</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1633414493426031</v>
+        <v>0.1629180874990865</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.3776041096483667</v>
+        <v>0.3733184413260986</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2559392964879024</v>
+        <v>0.2536292930818647</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2616605129568867</v>
+        <v>0.2577323489065719</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.08899511534921345</v>
+        <v>0.08546644030700179</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.271571943529807</v>
+        <v>0.2659323162373894</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.3539362119771212</v>
+        <v>0.3463262685491202</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.2401570384251244</v>
+        <v>0.2328261727778127</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.391020289540549</v>
+        <v>0.3816793893129855</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.4192159362627592</v>
+        <v>0.4081271002188132</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.5063429404948039</v>
+        <v>0.4934525516577608</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.02658</t>
+          <t>X &lt; 0.02656</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3973</v>
+        <v>3983</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.02231091262165563</v>
+        <v>-0.007609322384482198</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.0860660068911514</v>
+        <v>0.09945201611486709</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.08139958401626046</v>
+        <v>0.09484591085627159</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1500049116599556</v>
+        <v>0.163267861614969</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3034548495929883</v>
+        <v>0.3139286431877863</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2379045870320127</v>
+        <v>0.2497460639463966</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1920976118048472</v>
+        <v>0.2028301633282581</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.09066716149870757</v>
+        <v>0.1017096347653776</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.2446774660248963</v>
+        <v>0.2541055825402339</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2636183635632321</v>
+        <v>0.271859939653659</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2491395046510476</v>
+        <v>0.2574417089912515</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.272577804052176</v>
+        <v>0.279578955434026</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3195892921212646</v>
+        <v>0.3252810813763247</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.3583051353997675</v>
+        <v>0.3626330760145819</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02884</t>
+          <t>X &lt; 0.02882</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4021</v>
+        <v>4032</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.07635480098551994</v>
+        <v>-0.07500675690182135</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.03633824337429559</v>
+        <v>0.03628576849327203</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.002213793234083994</v>
+        <v>0.002213764516561412</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.09634096790694002</v>
+        <v>0.09609811267405632</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.3159801962833697</v>
+        <v>0.3132219588465759</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3540370052965045</v>
+        <v>0.3521360949815744</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2084903999760925</v>
+        <v>0.206044438183504</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.2020353058907389</v>
+        <v>0.1995579648251038</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3038329253732215</v>
+        <v>0.3001379079037463</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3124269633224088</v>
+        <v>0.3076862363667345</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2459893912469653</v>
+        <v>0.2414066519670044</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2944145071602478</v>
+        <v>0.2887668557717404</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.3358561405094918</v>
+        <v>0.3291149141037266</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.3022002398392019</v>
+        <v>0.2946357540629521</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.0311</t>
+          <t>X &lt; 0.03108</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4054</v>
+        <v>4065</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.009807105036443886</v>
+        <v>-0.008885733665799478</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.03972276572793731</v>
+        <v>0.03965197786494201</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.02192885890673324</v>
+        <v>-0.02186497490318118</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1216980919280601</v>
+        <v>0.1213847502191001</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.261350538944761</v>
+        <v>0.2591553754938332</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3261190265948173</v>
+        <v>0.324503022320016</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2056843833874638</v>
+        <v>0.2036549167639166</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.1462236111846806</v>
+        <v>0.1443163635741911</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1974108477396257</v>
+        <v>0.1946273936738763</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1743544801666701</v>
+        <v>0.1708311783864644</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1314069818335994</v>
+        <v>0.1279817160266816</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.1796895602205311</v>
+        <v>0.1754017159149157</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.2420073274768555</v>
+        <v>0.2367814853532764</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2597737436212029</v>
+        <v>0.253781774094584</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.03336</t>
+          <t>X &lt; 0.03334</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.02189963709172815</v>
+        <v>-0.02109279121201979</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.06844608981347022</v>
+        <v>0.06829273506333777</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.02965035945583594</v>
+        <v>0.02957466414245857</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1487385108472878</v>
+        <v>0.1483516483516425</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2605849819680017</v>
+        <v>0.2586397556912488</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3019951514609645</v>
+        <v>0.3005689421754028</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1572258750273576</v>
+        <v>0.1555712535905656</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1692845597020209</v>
+        <v>0.1675653897660467</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.146380026972075</v>
+        <v>0.1441056561105754</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.09473408622700674</v>
+        <v>0.09192813266760425</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.07550140428037366</v>
+        <v>0.07273211386230827</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1237020410338019</v>
+        <v>0.1201911852326418</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1590982475709666</v>
+        <v>0.1548489858871775</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.2024111722086133</v>
+        <v>0.197445103016733</v>
       </c>
     </row>
   </sheetData>
